--- a/Results/Phase 2/Hydrogen/hydrogen human toxicity non-carcinogenic results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen human toxicity non-carcinogenic results.xlsx
@@ -886,7 +886,7 @@
         <v>1.056443291441572e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.272530204171198e-07</v>
+        <v>1.056443291441573e-08</v>
       </c>
       <c r="O5" t="n">
         <v>1.056443291441573e-08</v>
@@ -974,7 +974,7 @@
         <v>4.496631655178622e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.272530204171198e-07</v>
+        <v>2.725399594972186e-08</v>
       </c>
       <c r="O6" t="n">
         <v>2.725401429814269e-08</v>
@@ -1062,7 +1062,7 @@
         <v>5.206590092530228e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.272530204171198e-07</v>
+        <v>5.206590092530228e-08</v>
       </c>
       <c r="O7" t="n">
         <v>5.206317353381056e-08</v>
@@ -1150,7 +1150,7 @@
         <v>2.606124384030903e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.272530204171198e-07</v>
+        <v>1.841371418422401e-07</v>
       </c>
       <c r="O8" t="n">
         <v>2.051532173685855e-07</v>
@@ -1238,7 +1238,7 @@
         <v>1.746496716537629e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>2.272530204171198e-07</v>
+        <v>1.746496716537629e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.867085642607923e-07</v>
@@ -1922,7 +1922,7 @@
         <v>9.36477122826826e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.447088091876593e-07</v>
+        <v>9.364771228268255e-09</v>
       </c>
       <c r="O5" t="n">
         <v>9.364771228268255e-09</v>
@@ -2010,7 +2010,7 @@
         <v>2.315428107172001e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.447088091876593e-07</v>
+        <v>2.317795177813879e-08</v>
       </c>
       <c r="O6" t="n">
         <v>3.703956301733775e-08</v>
@@ -2062,43 +2062,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="J7" t="n">
         <v>4.500371660857663e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.447088091876593e-07</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="O7" t="n">
         <v>4.505315619100463e-08</v>
@@ -2107,16 +2107,16 @@
         <v>4.505315619100463e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="U7" t="n">
         <v>4.505934585049921e-08</v>
@@ -2125,22 +2125,22 @@
         <v>4.4796831218739e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.505551947643012e-08</v>
+        <v>4.505551947643013e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2186,7 +2186,7 @@
         <v>2.249802134192712e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.447088091876593e-07</v>
+        <v>1.590509484370164e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.771688829150358e-07</v>
@@ -2274,7 +2274,7 @@
         <v>1.215381453984311e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.447088091876593e-07</v>
+        <v>1.215381453984311e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.298281062497298e-07</v>
@@ -2870,7 +2870,7 @@
         <v>1.072192895049694e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.094846361198606e-07</v>
+        <v>2.094846361198607e-07</v>
       </c>
       <c r="O4" t="n">
         <v>2.86100044315029e-07</v>
@@ -2958,7 +2958,7 @@
         <v>1.010357471031228e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>2.094846361198607e-07</v>
+        <v>1.010357471031227e-08</v>
       </c>
       <c r="O5" t="n">
         <v>1.010357471031227e-08</v>
@@ -3046,7 +3046,7 @@
         <v>4.198176255287927e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.094846361198606e-07</v>
+        <v>2.547398156495655e-08</v>
       </c>
       <c r="O6" t="n">
         <v>2.54730422206782e-08</v>
@@ -3134,7 +3134,7 @@
         <v>4.896372099857057e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.094846361198606e-07</v>
+        <v>4.896372099857057e-08</v>
       </c>
       <c r="O7" t="n">
         <v>4.896118420500679e-08</v>
@@ -3222,7 +3222,7 @@
         <v>2.441602293071678e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.094846361198606e-07</v>
+        <v>1.725635649867414e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.922389500124444e-07</v>
@@ -3310,7 +3310,7 @@
         <v>1.519531759095044e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>2.094846361198606e-07</v>
+        <v>1.519531759095044e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.624007688422457e-07</v>
@@ -3694,73 +3694,73 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.159177845444655e-08</v>
+        <v>3.159177845444653e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>3.061080349765871e-08</v>
+        <v>3.061080349765868e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>3.153110772414396e-08</v>
+        <v>3.153110772414393e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.213533454400649e-08</v>
+        <v>2.213533454400646e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>3.094632791653205e-08</v>
+        <v>3.094632791653203e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.219022080218794e-08</v>
+        <v>3.219022080218788e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.06826419273138e-08</v>
+        <v>3.068264192731376e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>3.105473199010886e-08</v>
+        <v>3.105473199010884e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.177162668667423e-08</v>
+        <v>3.17716266866742e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.115459573985999e-08</v>
+        <v>3.115459573985998e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.252620072534264e-08</v>
+        <v>3.252620072534263e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>3.346119743842226e-08</v>
+        <v>3.346119743842219e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.081873326737552e-08</v>
+        <v>3.081873326737551e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1115052322827e-08</v>
+        <v>3.111505232282697e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>3.17528941088914e-08</v>
+        <v>3.175289410889139e-08</v>
       </c>
       <c r="Q2" t="n">
         <v>3.093957318124666e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>3.067936321471184e-08</v>
+        <v>3.067936321471183e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>3.178708852111018e-08</v>
+        <v>3.17870885211102e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>3.090194283047449e-08</v>
+        <v>3.090194283047445e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>3.257603548734948e-08</v>
+        <v>3.257603548734947e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>2.426136263580685e-08</v>
+        <v>2.426136263580693e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>3.116648136535998e-08</v>
+        <v>3.116648136535996e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.204015751475247e-08</v>
+        <v>3.204015751475246e-08</v>
       </c>
       <c r="Y2" t="n">
         <v>3.25064430122425e-08</v>
@@ -3769,7 +3769,7 @@
         <v>3.1253753158911e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.106395654159923e-08</v>
+        <v>3.106395654159921e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>3.515597718766983e-08</v>
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="E3" t="n">
         <v>2.187139019377063e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.062368103007644e-08</v>
+        <v>3.062368103007641e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="V3" t="n">
         <v>2.371256436708019e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.068101690323755e-08</v>
+        <v>3.068101690323752e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.068101690340172e-08</v>
+        <v>3.068101690340169e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.556208299845443e-07</v>
+        <v>3.556208299845447e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.356522402288992e-07</v>
+        <v>1.35652240228899e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>3.718394761606569e-07</v>
+        <v>3.71839476160657e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.246565379934403e-07</v>
+        <v>1.246565379934399e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.212878473031128e-07</v>
+        <v>2.212878473031126e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.963729026325305e-07</v>
+        <v>4.963729026325313e-07</v>
       </c>
       <c r="H4" t="n">
         <v>1.540146082665842e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.492014581030231e-07</v>
+        <v>2.492014581030225e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.269536235320986e-07</v>
+        <v>4.269536235320989e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.666529603990971e-07</v>
+        <v>2.666529603990969e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.045202912773063e-07</v>
+        <v>6.045202912773037e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>8.929516533249907e-07</v>
+        <v>8.929516533249886e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.809472060526753e-07</v>
+        <v>1.809472060526754e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.408047781923311e-07</v>
+        <v>2.408047781923315e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>3.910895005323768e-07</v>
+        <v>3.910895005323763e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.122570951802519e-07</v>
+        <v>2.122570951802511e-07</v>
       </c>
       <c r="R4" t="n">
         <v>1.500249685210783e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>4.039085320039797e-07</v>
+        <v>4.039085320039788e-07</v>
       </c>
       <c r="T4" t="n">
         <v>2.071654445289576e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>6.039184680569429e-07</v>
+        <v>6.03918468056956e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>2.455599262858e-07</v>
+        <v>2.455599262858019e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>2.664407818820202e-07</v>
+        <v>2.664407818820195e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>4.996603357220042e-07</v>
+        <v>4.99660335722005e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.039109080950311e-07</v>
+        <v>6.039109080950306e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.704274108918832e-07</v>
+        <v>2.704274108918826e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.412864671357791e-07</v>
+        <v>2.412864671357783e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.404527526661841e-06</v>
+        <v>1.404527526661839e-06</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.014483628806101e-08</v>
+        <v>1.014483628806097e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0144836288061e-08</v>
+        <v>1.014483628806095e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0144836288061e-08</v>
+        <v>1.014483628806095e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0144836288061e-08</v>
+        <v>1.014483628806095e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.014483628806101e-08</v>
+        <v>1.014483628806097e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0144836288061e-08</v>
+        <v>1.014483628806095e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0144836288061e-08</v>
+        <v>1.014483628806095e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0144836288061e-08</v>
+        <v>1.014483628806095e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.008641890962588e-08</v>
+        <v>1.008641890962585e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0144836288061e-08</v>
+        <v>1.014483628806095e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.014483628806101e-08</v>
+        <v>1.014483628806096e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0144836288061e-08</v>
+        <v>1.014483628806095e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.809472060526753e-07</v>
+        <v>1.014483628806097e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.014483628806101e-08</v>
+        <v>1.014483628806097e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.014483628806101e-08</v>
+        <v>1.014483628806097e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.014483628806101e-08</v>
+        <v>1.014483628806097e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0144836288061e-08</v>
+        <v>1.014483628806095e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0144836288061e-08</v>
+        <v>1.014483628806095e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0144836288061e-08</v>
+        <v>1.014483628806095e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>9.947235292545794e-09</v>
+        <v>9.947235292545763e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>9.843905186069764e-09</v>
+        <v>9.843905186069737e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.014483628806101e-08</v>
+        <v>1.014483628806097e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.014483628806101e-08</v>
+        <v>1.014483628806097e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.947235292545794e-09</v>
+        <v>9.947235292545763e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.0144836288061e-08</v>
+        <v>1.014483628806095e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.0144836288061e-08</v>
+        <v>1.014483628806095e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.014483628806101e-08</v>
+        <v>1.014483628806097e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.987103672183121e-08</v>
+        <v>3.987103672183126e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.442047462164802e-08</v>
+        <v>2.442047462164794e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.987103672183121e-08</v>
+        <v>3.987103672183125e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.987103672183121e-08</v>
+        <v>3.987103672183125e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.442047462164802e-08</v>
+        <v>2.442047462164794e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.442047462164802e-08</v>
+        <v>2.442047462164794e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.442047462164802e-08</v>
+        <v>2.442047462164794e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.442047462164802e-08</v>
+        <v>2.442047462164794e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.981261934339602e-08</v>
+        <v>3.981261934339616e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.987103672183121e-08</v>
+        <v>3.987103672183125e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.987103672183121e-08</v>
+        <v>3.987103672183126e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.442047462164802e-08</v>
+        <v>2.442047462164794e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.809472060526753e-07</v>
+        <v>2.447801438497686e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.996115765644049e-08</v>
+        <v>3.996115765644033e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.996209624952146e-08</v>
+        <v>3.996209624952138e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.987103672183121e-08</v>
+        <v>3.987103672183125e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>2.442047462164802e-08</v>
+        <v>2.442047462164794e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.987103672183121e-08</v>
+        <v>3.987103672183125e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.442047462164802e-08</v>
+        <v>2.442047462164794e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.442047462164802e-08</v>
+        <v>2.442047462164794e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.957010561984003e-08</v>
+        <v>3.957010561984004e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>3.996087026947224e-08</v>
+        <v>3.996087026947219e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>2.442047462164802e-08</v>
+        <v>2.442047462164794e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.519295383051665e-08</v>
+        <v>2.519295383051675e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.987103672183121e-08</v>
+        <v>3.987103672183125e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.987103672183121e-08</v>
+        <v>3.987103672183125e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.478057779915055e-08</v>
+        <v>2.478057779915052e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.665285965146588e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>4.65944422730309e-08</v>
+        <v>4.65944422730308e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>4.665285965146588e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.809472060526753e-07</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>4.665048625815909e-08</v>
+        <v>4.665048625815904e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.665048625815909e-08</v>
+        <v>4.665048625815904e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>4.664867103377547e-08</v>
+        <v>4.664867103377539e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>4.635192854947469e-08</v>
+        <v>4.635192854947468e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.665285965146588e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.665285965146586e-08</v>
+        <v>4.665285965146592e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4222,43 +4222,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.42479236584967e-07</v>
+        <v>1.424792365849671e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.288178658417662e-07</v>
+        <v>2.288178658417664e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.288178658417662e-07</v>
+        <v>2.288178658417664e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.82845092590231e-07</v>
+        <v>1.828450925902309e-07</v>
       </c>
       <c r="F8" t="n">
         <v>1.559297859636757e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.467207430629472e-07</v>
+        <v>2.467207430629468e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.288178658417662e-07</v>
+        <v>2.288178658417664e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.288178658417662e-07</v>
+        <v>2.288178658417664e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.287594484633315e-07</v>
+        <v>2.287594484633313e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.288178658417662e-07</v>
+        <v>2.288178658417664e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.288178658417663e-07</v>
+        <v>2.288178658417665e-07</v>
       </c>
       <c r="M8" t="n">
         <v>2.288178658417683e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.809472060526753e-07</v>
+        <v>1.618909840328252e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.802830722768015e-07</v>
@@ -4267,40 +4267,40 @@
         <v>1.757747270323457e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.255117253495949e-07</v>
+        <v>1.25511725349595e-07</v>
       </c>
       <c r="R8" t="n">
-        <v>2.288178658417662e-07</v>
+        <v>2.288178658417664e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>2.288178658417662e-07</v>
+        <v>2.288178658417664e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>2.288178658417662e-07</v>
+        <v>2.288178658417664e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>1.866757265032923e-07</v>
+        <v>1.866757265032924e-07</v>
       </c>
       <c r="V8" t="n">
-        <v>2.049177339333268e-07</v>
+        <v>2.049177339333269e-07</v>
       </c>
       <c r="W8" t="n">
-        <v>2.28834833868604e-07</v>
+        <v>2.288348338686038e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.334248322860297e-07</v>
+        <v>1.334248322860299e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.146599931736319e-07</v>
+        <v>3.146599931736317e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.408754522190736e-07</v>
+        <v>1.408754522190737e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.288178658417662e-07</v>
+        <v>2.288178658417664e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.190057836308534e-07</v>
+        <v>3.190057836308535e-07</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.071344438005523e-07</v>
+        <v>1.071344438005521e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.285217121810144e-07</v>
+        <v>1.285217121810143e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>7.084209546194466e-08</v>
+        <v>7.084209546194447e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.349388574359198e-07</v>
+        <v>1.349388574359195e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="J9" t="n">
         <v>1.34880436586135e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="L9" t="n">
         <v>1.349388539645701e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.809472060526753e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>1.441532037079135e-07</v>
+        <v>1.44153203707913e-07</v>
       </c>
       <c r="P9" t="n">
-        <v>1.461571659305107e-07</v>
+        <v>1.461571659305106e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.349388574359198e-07</v>
+        <v>1.349388574359195e-07</v>
       </c>
       <c r="R9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="T9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="V9" t="n">
-        <v>1.66723590930465e-07</v>
+        <v>1.667235909304648e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="X9" t="n">
         <v>1.349388539645701e-07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.181752684787231e-07</v>
+        <v>1.181752684787229e-07</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.349388539645702e-07</v>
+        <v>1.3493885396457e-07</v>
       </c>
     </row>
     <row r="10">
@@ -4398,85 +4398,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.392097407203417e-08</v>
+        <v>2.392097407203413e-08</v>
       </c>
       <c r="C10" t="n">
-        <v>2.977221197294796e-08</v>
+        <v>2.977221197294795e-08</v>
       </c>
       <c r="D10" t="n">
-        <v>2.438270769930369e-08</v>
+        <v>2.438270769930368e-08</v>
       </c>
       <c r="E10" t="n">
-        <v>1.944525225569457e-08</v>
+        <v>1.944525225569456e-08</v>
       </c>
       <c r="F10" t="n">
         <v>2.782281376394647e-08</v>
       </c>
       <c r="G10" t="n">
-        <v>2.036656423729547e-08</v>
+        <v>2.03665642372954e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>2.936260654852425e-08</v>
+        <v>2.936260654852423e-08</v>
       </c>
       <c r="I10" t="n">
-        <v>2.717992971191462e-08</v>
+        <v>2.717992971191459e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>2.250636612177686e-08</v>
+        <v>2.250636612177687e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>2.658214104374894e-08</v>
+        <v>2.658214104374891e-08</v>
       </c>
       <c r="L10" t="n">
-        <v>1.844014516926948e-08</v>
+        <v>1.844014516926951e-08</v>
       </c>
       <c r="M10" t="n">
-        <v>1.314449747700035e-08</v>
+        <v>1.314449747700033e-08</v>
       </c>
       <c r="N10" t="n">
-        <v>2.854586874144073e-08</v>
+        <v>2.854586874144072e-08</v>
       </c>
       <c r="O10" t="n">
-        <v>2.675266291314737e-08</v>
+        <v>2.675266291314735e-08</v>
       </c>
       <c r="P10" t="n">
-        <v>2.29469161544706e-08</v>
+        <v>2.294691615447057e-08</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.784001966166362e-08</v>
+        <v>2.784001966166359e-08</v>
       </c>
       <c r="R10" t="n">
-        <v>2.93775595853882e-08</v>
+        <v>2.937755958538814e-08</v>
       </c>
       <c r="S10" t="n">
-        <v>2.278394399612984e-08</v>
+        <v>2.278394399612978e-08</v>
       </c>
       <c r="T10" t="n">
-        <v>2.806981551307279e-08</v>
+        <v>2.806981551307276e-08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.813287502575993e-08</v>
+        <v>1.813287502575982e-08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.974301829580139e-08</v>
+        <v>1.974301829580144e-08</v>
       </c>
       <c r="W10" t="n">
-        <v>2.648583136153823e-08</v>
+        <v>2.648583136153824e-08</v>
       </c>
       <c r="X10" t="n">
-        <v>2.139184972568541e-08</v>
+        <v>2.139184972568544e-08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.859718933090145e-08</v>
+        <v>1.859718933090143e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.593737326942675e-08</v>
+        <v>2.593737326942672e-08</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.7093987091407e-08</v>
+        <v>2.709398709140701e-08</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.156169727391935e-09</v>
+        <v>3.156169727391937e-09</v>
       </c>
     </row>
     <row r="11">
@@ -4486,85 +4486,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.851593742319602e-08</v>
+        <v>2.851593742319601e-08</v>
       </c>
       <c r="C11" t="n">
         <v>3.019729435811276e-08</v>
       </c>
       <c r="D11" t="n">
-        <v>2.866535696475884e-08</v>
+        <v>2.866535696475883e-08</v>
       </c>
       <c r="E11" t="n">
-        <v>2.1031434050539e-08</v>
+        <v>2.103143405053898e-08</v>
       </c>
       <c r="F11" t="n">
         <v>2.964583637952695e-08</v>
       </c>
       <c r="G11" t="n">
-        <v>2.749711196889921e-08</v>
+        <v>2.74971119688992e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>3.008276101432e-08</v>
+        <v>3.008276101431998e-08</v>
       </c>
       <c r="I11" t="n">
-        <v>2.946172616067934e-08</v>
+        <v>2.946172616067935e-08</v>
       </c>
       <c r="J11" t="n">
         <v>2.807822253505019e-08</v>
       </c>
       <c r="K11" t="n">
-        <v>2.928959416137566e-08</v>
+        <v>2.928959416137563e-08</v>
       </c>
       <c r="L11" t="n">
         <v>2.695656507696885e-08</v>
       </c>
       <c r="M11" t="n">
-        <v>2.548202521383811e-08</v>
+        <v>2.548202521383808e-08</v>
       </c>
       <c r="N11" t="n">
-        <v>2.984723404936981e-08</v>
+        <v>2.984723404936978e-08</v>
       </c>
       <c r="O11" t="n">
-        <v>2.932763873833987e-08</v>
+        <v>2.93276387383399e-08</v>
       </c>
       <c r="P11" t="n">
-        <v>2.823385362101106e-08</v>
+        <v>2.823385362101102e-08</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.964691038253485e-08</v>
+        <v>2.964691038253482e-08</v>
       </c>
       <c r="R11" t="n">
-        <v>3.008628598114368e-08</v>
+        <v>3.008628598114366e-08</v>
       </c>
       <c r="S11" t="n">
-        <v>2.81938951818234e-08</v>
+        <v>2.819389518182339e-08</v>
       </c>
       <c r="T11" t="n">
-        <v>2.971383787646974e-08</v>
+        <v>2.97138378764697e-08</v>
       </c>
       <c r="U11" t="n">
-        <v>2.686659094446699e-08</v>
+        <v>2.686659094446701e-08</v>
       </c>
       <c r="V11" t="n">
-        <v>2.245520652318226e-08</v>
+        <v>2.245520652318234e-08</v>
       </c>
       <c r="W11" t="n">
-        <v>2.925765857454902e-08</v>
+        <v>2.925765857454901e-08</v>
       </c>
       <c r="X11" t="n">
-        <v>2.781355684607219e-08</v>
+        <v>2.78135568460722e-08</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.700826295795599e-08</v>
+        <v>2.700826295795598e-08</v>
       </c>
       <c r="Z11" t="n">
         <v>2.909538018835706e-08</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.943184654595588e-08</v>
+        <v>2.943184654595587e-08</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.263208400610206e-08</v>
+        <v>2.263208400610202e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4730,85 +4730,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.160010575781613e-08</v>
+        <v>3.160010575781614e-08</v>
       </c>
       <c r="C2" t="n">
         <v>3.078666031485921e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>3.15004096919975e-08</v>
+        <v>3.150040969199753e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.204157386019143e-08</v>
+        <v>2.204157386019144e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>3.117884196775379e-08</v>
+        <v>3.117884196775375e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.215546163800782e-08</v>
+        <v>3.215546163800785e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.086203487734686e-08</v>
+        <v>3.086203487734688e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>3.121240425437226e-08</v>
+        <v>3.121240425437229e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.186107141045609e-08</v>
+        <v>3.18610714104561e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.140300282051525e-08</v>
+        <v>3.140300282051526e-08</v>
       </c>
       <c r="L2" t="n">
         <v>3.234350504327618e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>3.31624819083719e-08</v>
+        <v>3.316248190837189e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.092842817088259e-08</v>
+        <v>3.092842817088263e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>3.109193082997987e-08</v>
+        <v>3.109193082997988e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>3.181388587385279e-08</v>
+        <v>3.181388587385278e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.113174068088723e-08</v>
+        <v>3.113174068088724e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>3.093940887498248e-08</v>
+        <v>3.093940887498247e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>3.185204385271449e-08</v>
+        <v>3.185204385271453e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>3.112447561556949e-08</v>
+        <v>3.112447561556947e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>3.276082254870883e-08</v>
+        <v>3.276082254870886e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>2.509912711780046e-08</v>
+        <v>2.509912711780048e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>3.137101509059437e-08</v>
+        <v>3.137101509059435e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.235054798483331e-08</v>
+        <v>3.235054798483332e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.377088596138182e-08</v>
+        <v>3.377088596138178e-08</v>
       </c>
       <c r="Z2" t="n">
         <v>3.137189002950941e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.128882932842738e-08</v>
+        <v>3.12888293284274e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.488551964799255e-08</v>
+        <v>3.488551964799257e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.187021982545262e-08</v>
+        <v>2.187021982545264e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="J3" t="n">
         <v>3.080871439208777e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.416848276695161e-08</v>
+        <v>2.416848276695158e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.084332358574774e-08</v>
+        <v>3.084332358574776e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.084332358603594e-08</v>
+        <v>3.084332358603596e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4906,85 +4906,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.150217145295062e-07</v>
+        <v>3.150217145295069e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.400049994144452e-07</v>
+        <v>1.400049994144448e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>3.174657018505537e-07</v>
+        <v>3.174657018505568e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.044225040387988e-07</v>
+        <v>1.044225040387989e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.393947034673764e-07</v>
+        <v>2.393947034673742e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.42065421418595e-07</v>
+        <v>4.420654214185933e-07</v>
       </c>
       <c r="H4" t="n">
         <v>1.590545471948365e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.481434333894648e-07</v>
+        <v>2.481434333894644e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>3.982165679280365e-07</v>
+        <v>3.982165679280344e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.868676893589903e-07</v>
+        <v>2.868676893589897e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>5.060846312383885e-07</v>
+        <v>5.060846312383883e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>7.460946142505624e-07</v>
+        <v>7.460946142505608e-07</v>
       </c>
       <c r="N4" t="n">
         <v>1.679578788102534e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.996529128099231e-07</v>
+        <v>1.996529128099228e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>3.613808460250951e-07</v>
+        <v>3.613808460250929e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.188238230504012e-07</v>
+        <v>2.188238230504011e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.77156766551352e-07</v>
+        <v>1.771567665513515e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>3.782945315451671e-07</v>
+        <v>3.782945315451693e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.237213315390765e-07</v>
+        <v>2.237213315390767e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>5.946881865033856e-07</v>
+        <v>5.946881865033849e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>3.305486747699078e-07</v>
+        <v>3.305486747699063e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>2.778359344677981e-07</v>
+        <v>2.77835934467798e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>5.267320179154404e-07</v>
+        <v>5.267320179154378e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.954512339760781e-07</v>
+        <v>8.954512339760734e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.558296340780656e-07</v>
+        <v>2.558296340780658e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.579460061881149e-07</v>
+        <v>2.579460061881141e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.267309747061437e-06</v>
+        <v>1.267309747061434e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.055909134181449e-08</v>
+        <v>1.055909134181457e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.055909134181447e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.055909134181447e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.055909134181447e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.055909134181448e-08</v>
+        <v>1.055909134181453e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.055909134181447e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.055909134181447e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.055909134181447e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.050550032360704e-08</v>
+        <v>1.050550032360711e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.055909134181447e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.055909134181448e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>1.055909134181447e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>1.679578788102534e-07</v>
+        <v>1.055909134181453e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>1.055909134181448e-08</v>
+        <v>1.055909134181453e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.055909134181448e-08</v>
+        <v>1.055909134181453e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.055909134181448e-08</v>
+        <v>1.055909134181453e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>1.055909134181447e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.055909134181447e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>1.055909134181447e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.047785259741872e-08</v>
+        <v>1.047785259741879e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>1.028903633513364e-08</v>
+        <v>1.028903633513362e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.055909134181448e-08</v>
+        <v>1.055909134181453e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.055909134181449e-08</v>
+        <v>1.055909134181453e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.047785259741872e-08</v>
+        <v>1.047785259741879e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.055909134181447e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.055909134181447e-08</v>
+        <v>1.05590913418146e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.055909134181448e-08</v>
+        <v>1.055909134181453e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5088,10 +5088,10 @@
         <v>2.49977171243865e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>4.035674236022383e-08</v>
+        <v>4.035674236022392e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>4.035674236022383e-08</v>
+        <v>4.035674236022392e-08</v>
       </c>
       <c r="F6" t="n">
         <v>2.49977171243865e-08</v>
@@ -5100,16 +5100,16 @@
         <v>2.49977171243865e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>4.035674236022383e-08</v>
+        <v>4.035674236022392e-08</v>
       </c>
       <c r="I6" t="n">
         <v>2.49977171243865e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>4.030315134201637e-08</v>
+        <v>4.030315134201629e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>4.035674236022383e-08</v>
+        <v>4.035674236022392e-08</v>
       </c>
       <c r="L6" t="n">
         <v>2.49977171243865e-08</v>
@@ -5118,49 +5118,49 @@
         <v>2.49977171243865e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.679578788102534e-07</v>
+        <v>2.508173196844955e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5081422508245e-08</v>
+        <v>2.508142250824529e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>4.04592234218109e-08</v>
+        <v>4.045922342181113e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.035674236022383e-08</v>
+        <v>4.035674236022392e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>4.035674236022383e-08</v>
+        <v>4.035674236022392e-08</v>
       </c>
       <c r="S6" t="n">
         <v>2.49977171243865e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>4.035674236022383e-08</v>
+        <v>4.035674236022392e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>4.035674236022383e-08</v>
+        <v>4.035674236022392e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>2.472766211770574e-08</v>
+        <v>2.472766211770553e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>2.58921253439464e-08</v>
+        <v>2.589212534394637e-08</v>
       </c>
       <c r="X6" t="n">
         <v>2.49977171243865e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.582821707819872e-08</v>
+        <v>2.582821707819869e-08</v>
       </c>
       <c r="Z6" t="n">
         <v>2.49977171243865e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.035674236022383e-08</v>
+        <v>4.035674236022392e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.532952367929937e-08</v>
+        <v>2.532952367929947e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.727636635428125e-08</v>
+        <v>4.727636635428121e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>4.722277533607373e-08</v>
+        <v>4.722277533607377e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>4.727636635428125e-08</v>
+        <v>4.727636635428121e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.679578788102534e-07</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>4.72739807425637e-08</v>
+        <v>4.727398074256367e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>4.72739807425637e-08</v>
+        <v>4.727398074256367e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>4.728241023323168e-08</v>
+        <v>4.728241023323156e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>4.700631134760042e-08</v>
+        <v>4.700631134760025e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>4.727636635428125e-08</v>
+        <v>4.727636635428121e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.727636635428123e-08</v>
+        <v>4.72763663542812e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5258,85 +5258,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.430610248747976e-07</v>
+        <v>1.430610248747972e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.2955129773884e-07</v>
+        <v>2.295512977388396e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2955129773884e-07</v>
+        <v>2.295512977388396e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>1.834977787396626e-07</v>
+        <v>1.834977787396622e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>1.565351985552099e-07</v>
+        <v>1.565351985552094e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.474856192498419e-07</v>
+        <v>2.474856192498413e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2955129773884e-07</v>
+        <v>2.295512977388396e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2955129773884e-07</v>
+        <v>2.295512977388396e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>2.294977067206326e-07</v>
+        <v>2.294977067206324e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2955129773884e-07</v>
+        <v>2.295512977388396e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2955129773884e-07</v>
+        <v>2.295512977388395e-07</v>
       </c>
       <c r="M8" t="n">
-        <v>2.295512977388435e-07</v>
+        <v>2.295512977388431e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.679578788102534e-07</v>
+        <v>1.625068667648451e-07</v>
       </c>
       <c r="O8" t="n">
-        <v>1.809312585400106e-07</v>
+        <v>1.809312585400101e-07</v>
       </c>
       <c r="P8" t="n">
-        <v>1.764149949195005e-07</v>
+        <v>1.764149949195002e-07</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.260637122095185e-07</v>
+        <v>1.260637122095184e-07</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2955129773884e-07</v>
+        <v>2.295512977388396e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2955129773884e-07</v>
+        <v>2.295512977388396e-07</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2955129773884e-07</v>
+        <v>2.295512977388396e-07</v>
       </c>
       <c r="U8" t="n">
-        <v>1.873430825822752e-07</v>
+        <v>1.873430825822749e-07</v>
       </c>
       <c r="V8" t="n">
-        <v>2.056493523701038e-07</v>
+        <v>2.056493523701034e-07</v>
       </c>
       <c r="W8" t="n">
-        <v>2.295682955679324e-07</v>
+        <v>2.29568295567932e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.339907175838431e-07</v>
+        <v>1.339907175838429e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.155577828657928e-07</v>
+        <v>3.155577828657924e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.414544236510484e-07</v>
+        <v>1.414544236510481e-07</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.2955129773884e-07</v>
+        <v>2.295512977388396e-07</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.198976199558766e-07</v>
+        <v>3.198976199558759e-07</v>
       </c>
     </row>
     <row r="9">
@@ -5346,85 +5346,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.02904401277808e-07</v>
+        <v>1.029044012778079e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="D9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="E9" t="n">
-        <v>1.233188320143331e-07</v>
+        <v>1.233188320143329e-07</v>
       </c>
       <c r="F9" t="n">
-        <v>6.826287444770723e-08</v>
+        <v>6.826287444770717e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>1.294440820931211e-07</v>
+        <v>1.294440820931209e-07</v>
       </c>
       <c r="H9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="I9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>1.293904870558437e-07</v>
+        <v>1.293904870558435e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="M9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.679578788102534e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38239297564575e-07</v>
+        <v>1.382392975645748e-07</v>
       </c>
       <c r="P9" t="n">
-        <v>1.401521060291281e-07</v>
+        <v>1.401521060291279e-07</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.294440820931211e-07</v>
+        <v>1.294440820931209e-07</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="S9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="T9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="V9" t="n">
-        <v>1.598002190167364e-07</v>
+        <v>1.598002190167359e-07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.134430145619868e-07</v>
+        <v>1.134430145619866e-07</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.29444078074051e-07</v>
+        <v>1.294440780740512e-07</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.49930988530919e-08</v>
+        <v>2.499309885309196e-08</v>
       </c>
       <c r="C10" t="n">
         <v>2.984891260402308e-08</v>
       </c>
       <c r="D10" t="n">
-        <v>2.566940898505867e-08</v>
+        <v>2.566940898505881e-08</v>
       </c>
       <c r="E10" t="n">
-        <v>2.000038622160064e-08</v>
+        <v>2.000038622160067e-08</v>
       </c>
       <c r="F10" t="n">
-        <v>2.756977844912214e-08</v>
+        <v>2.75697784491222e-08</v>
       </c>
       <c r="G10" t="n">
-        <v>2.16943695979707e-08</v>
+        <v>2.169436959797082e-08</v>
       </c>
       <c r="H10" t="n">
-        <v>2.941940927705137e-08</v>
+        <v>2.941940927705139e-08</v>
       </c>
       <c r="I10" t="n">
-        <v>2.736320664331003e-08</v>
+        <v>2.736320664331006e-08</v>
       </c>
       <c r="J10" t="n">
-        <v>2.325663515081328e-08</v>
+        <v>2.325663515081338e-08</v>
       </c>
       <c r="K10" t="n">
-        <v>2.623325167550069e-08</v>
+        <v>2.623325167550074e-08</v>
       </c>
       <c r="L10" t="n">
-        <v>2.063585721772953e-08</v>
+        <v>2.063585721772956e-08</v>
       </c>
       <c r="M10" t="n">
-        <v>1.599089479215407e-08</v>
+        <v>1.599089479215415e-08</v>
       </c>
       <c r="N10" t="n">
-        <v>2.90114919966108e-08</v>
+        <v>2.901149199661082e-08</v>
       </c>
       <c r="O10" t="n">
-        <v>2.801307651046419e-08</v>
+        <v>2.801307651046421e-08</v>
       </c>
       <c r="P10" t="n">
-        <v>2.370691104476591e-08</v>
+        <v>2.370691104476596e-08</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.78208162522176e-08</v>
+        <v>2.782081625221761e-08</v>
       </c>
       <c r="R10" t="n">
-        <v>2.896350038296781e-08</v>
+        <v>2.896350038296783e-08</v>
       </c>
       <c r="S10" t="n">
-        <v>2.351740980289132e-08</v>
+        <v>2.351740980289136e-08</v>
       </c>
       <c r="T10" t="n">
-        <v>2.787343716077822e-08</v>
+        <v>2.787343716077823e-08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.815594942427814e-08</v>
+        <v>1.815594942427812e-08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.790395222090165e-08</v>
+        <v>1.79039522209017e-08</v>
       </c>
       <c r="W10" t="n">
-        <v>2.639273226962193e-08</v>
+        <v>2.639273226962196e-08</v>
       </c>
       <c r="X10" t="n">
-        <v>2.067977394933843e-08</v>
+        <v>2.067977394933846e-08</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.225904644849435e-08</v>
+        <v>1.225904644849441e-08</v>
       </c>
       <c r="Z10" t="n">
         <v>2.635593766759976e-08</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.688115244698969e-08</v>
+        <v>2.688115244698971e-08</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.84669189043862e-09</v>
+        <v>5.846691890438624e-09</v>
       </c>
     </row>
     <row r="11">
@@ -5522,79 +5522,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.893823486076653e-08</v>
+        <v>2.893823486076656e-08</v>
       </c>
       <c r="C11" t="n">
         <v>3.033420014904358e-08</v>
       </c>
       <c r="D11" t="n">
-        <v>2.914626206026536e-08</v>
+        <v>2.914626206026541e-08</v>
       </c>
       <c r="E11" t="n">
-        <v>2.119079361163265e-08</v>
+        <v>2.119079361163267e-08</v>
       </c>
       <c r="F11" t="n">
-        <v>2.96893684982886e-08</v>
+        <v>2.968936849828864e-08</v>
       </c>
       <c r="G11" t="n">
-        <v>2.799265841745174e-08</v>
+        <v>2.799265841745179e-08</v>
       </c>
       <c r="H11" t="n">
-        <v>3.02141493290132e-08</v>
+        <v>3.021414932901322e-08</v>
       </c>
       <c r="I11" t="n">
         <v>2.962893995495732e-08</v>
       </c>
       <c r="J11" t="n">
-        <v>2.842485128862766e-08</v>
+        <v>2.842485128862769e-08</v>
       </c>
       <c r="K11" t="n">
-        <v>2.930540540979423e-08</v>
+        <v>2.930540540979424e-08</v>
       </c>
       <c r="L11" t="n">
         <v>2.769907531643154e-08</v>
       </c>
       <c r="M11" t="n">
-        <v>2.640457947527342e-08</v>
+        <v>2.640457947527345e-08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.009493895999325e-08</v>
+        <v>3.009493895999327e-08</v>
       </c>
       <c r="O11" t="n">
-        <v>2.980415939113245e-08</v>
+        <v>2.980415939113246e-08</v>
       </c>
       <c r="P11" t="n">
-        <v>2.856679542517752e-08</v>
+        <v>2.856679542517754e-08</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.975649021184055e-08</v>
+        <v>2.975649021184058e-08</v>
       </c>
       <c r="R11" t="n">
-        <v>3.008408332694536e-08</v>
+        <v>3.008408332694539e-08</v>
       </c>
       <c r="S11" t="n">
-        <v>2.851872973508174e-08</v>
+        <v>2.85187297350818e-08</v>
       </c>
       <c r="T11" t="n">
-        <v>2.977316782761076e-08</v>
+        <v>2.977316782761077e-08</v>
       </c>
       <c r="U11" t="n">
-        <v>2.698802687284659e-08</v>
+        <v>2.69880268728466e-08</v>
       </c>
       <c r="V11" t="n">
-        <v>2.224874575547341e-08</v>
+        <v>2.224874575547347e-08</v>
       </c>
       <c r="W11" t="n">
-        <v>2.934598185843301e-08</v>
+        <v>2.9345981858433e-08</v>
       </c>
       <c r="X11" t="n">
-        <v>2.772610051082505e-08</v>
+        <v>2.772610051082512e-08</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.53149806393543e-08</v>
+        <v>2.531498063935433e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.933011513617054e-08</v>
+        <v>2.933011513617056e-08</v>
       </c>
       <c r="AA11" t="n">
         <v>2.948602883347112e-08</v>
@@ -6066,7 +6066,7 @@
         <v>9.361116155231135e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.665714283592556e-07</v>
+        <v>9.36111615523114e-09</v>
       </c>
       <c r="O5" t="n">
         <v>9.36111615523114e-09</v>
@@ -6154,7 +6154,7 @@
         <v>3.928199413095718e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.665714283592556e-07</v>
+        <v>2.436541429116787e-08</v>
       </c>
       <c r="O6" t="n">
         <v>3.937982377737533e-08</v>
@@ -6242,7 +6242,7 @@
         <v>4.719265472718894e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.665714283592556e-07</v>
+        <v>4.719265472718894e-08</v>
       </c>
       <c r="O7" t="n">
         <v>4.719012293840678e-08</v>
@@ -6330,7 +6330,7 @@
         <v>2.399884517097643e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.665714283592556e-07</v>
+        <v>1.695271581799078e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.888905334542078e-07</v>
@@ -6418,7 +6418,7 @@
         <v>1.436710712604345e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.665714283592556e-07</v>
+        <v>1.436710712604345e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.535529139260709e-07</v>
@@ -7078,7 +7078,7 @@
         <v>9.220885989084022e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>9.220885989083991e-09</v>
+        <v>9.220885989083992e-09</v>
       </c>
       <c r="G5" t="n">
         <v>9.220885989084022e-09</v>
@@ -7102,16 +7102,16 @@
         <v>9.220885989084022e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.578604622573297e-07</v>
+        <v>9.220885989083989e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>9.220885989083991e-09</v>
+        <v>9.220885989083992e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>9.220885989083991e-09</v>
+        <v>9.220885989083992e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.220885989083991e-09</v>
+        <v>9.220885989083992e-09</v>
       </c>
       <c r="R5" t="n">
         <v>9.220885989084022e-09</v>
@@ -7132,7 +7132,7 @@
         <v>9.220885989083989e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>9.220885989083991e-09</v>
+        <v>9.220885989083992e-09</v>
       </c>
       <c r="Y5" t="n">
         <v>9.160292233686851e-09</v>
@@ -7144,7 +7144,7 @@
         <v>9.220885989084022e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.220885989083991e-09</v>
+        <v>9.220885989083992e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7190,7 +7190,7 @@
         <v>3.677175303141276e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.578604622573297e-07</v>
+        <v>2.307864753548877e-08</v>
       </c>
       <c r="O6" t="n">
         <v>3.686077227663444e-08</v>
@@ -7278,7 +7278,7 @@
         <v>4.462344248435709e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.578604622573297e-07</v>
+        <v>4.462344248435709e-08</v>
       </c>
       <c r="O7" t="n">
         <v>4.462108006485514e-08</v>
@@ -7366,7 +7366,7 @@
         <v>2.241204781328847e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.578604622573297e-07</v>
+        <v>1.58440717014339e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.764900856641467e-07</v>
@@ -7399,7 +7399,7 @@
         <v>1.305050057401776e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.083741386536704e-07</v>
+        <v>3.083741386536703e-07</v>
       </c>
       <c r="Z8" t="n">
         <v>1.378167902451237e-07</v>
@@ -7454,7 +7454,7 @@
         <v>1.264518259702657e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.578604622573297e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.350968106489944e-07</v>
@@ -7666,7 +7666,7 @@
         <v>2.840726374414311e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.882967570412754e-08</v>
+        <v>2.882967570412753e-08</v>
       </c>
       <c r="AA11" t="n">
         <v>2.872627491860041e-08</v>
@@ -8138,7 +8138,7 @@
         <v>9.372154760831015e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.474424641565742e-07</v>
+        <v>9.372154760831033e-09</v>
       </c>
       <c r="O5" t="n">
         <v>9.372154760831033e-09</v>
@@ -8226,7 +8226,7 @@
         <v>3.705281243414684e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.474424641565742e-07</v>
+        <v>2.320585994588314e-08</v>
       </c>
       <c r="O6" t="n">
         <v>2.320557384394975e-08</v>
@@ -8314,7 +8314,7 @@
         <v>4.501609041429935e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.474424641565742e-07</v>
+        <v>4.501609041429935e-08</v>
       </c>
       <c r="O7" t="n">
         <v>4.501372653496779e-08</v>
@@ -8402,7 +8402,7 @@
         <v>2.248279116202717e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.474424641565742e-07</v>
+        <v>1.589477807665306e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.770522127593055e-07</v>
@@ -8490,7 +8490,7 @@
         <v>1.216084750175946e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.474424641565742e-07</v>
+        <v>1.216084750175946e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.299027072551904e-07</v>
@@ -9086,7 +9086,7 @@
         <v>9.748346756322837e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>2.10631397790833e-07</v>
+        <v>2.106313977908331e-07</v>
       </c>
       <c r="O4" t="n">
         <v>2.076395411285191e-07</v>
@@ -9174,7 +9174,7 @@
         <v>9.916450345648528e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>2.106313977908331e-07</v>
+        <v>9.916450345648533e-09</v>
       </c>
       <c r="O5" t="n">
         <v>9.916450345648533e-09</v>
@@ -9262,7 +9262,7 @@
         <v>2.509291921515724e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.10631397790833e-07</v>
+        <v>2.513917064845308e-08</v>
       </c>
       <c r="O6" t="n">
         <v>4.152646247044492e-08</v>
@@ -9350,7 +9350,7 @@
         <v>4.849226996853606e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.10631397790833e-07</v>
+        <v>4.849226996853606e-08</v>
       </c>
       <c r="O7" t="n">
         <v>4.848973525698763e-08</v>
@@ -9438,7 +9438,7 @@
         <v>2.43088099709175e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>2.10631397790833e-07</v>
+        <v>1.717801520840454e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.913761952549809e-07</v>
@@ -9526,7 +9526,7 @@
         <v>1.505390607586835e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>2.10631397790833e-07</v>
+        <v>1.505390607586835e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.608932745971975e-07</v>
@@ -10210,7 +10210,7 @@
         <v>9.490875907915629e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.59264464159528e-07</v>
+        <v>9.490875907915626e-09</v>
       </c>
       <c r="O5" t="n">
         <v>9.490875907915626e-09</v>
@@ -10298,7 +10298,7 @@
         <v>2.329213709412209e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.59264464159528e-07</v>
+        <v>2.331591849401529e-08</v>
       </c>
       <c r="O6" t="n">
         <v>3.811046561410411e-08</v>
@@ -10386,7 +10386,7 @@
         <v>4.528085196134408e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.59264464159528e-07</v>
+        <v>4.528085196134408e-08</v>
       </c>
       <c r="O7" t="n">
         <v>4.527848834329094e-08</v>
@@ -10474,7 +10474,7 @@
         <v>2.258379165841912e-07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.59264464159528e-07</v>
+        <v>1.596654774662147e-07</v>
       </c>
       <c r="O8" t="n">
         <v>1.778502383080494e-07</v>
@@ -10562,7 +10562,7 @@
         <v>1.30664996357417e-07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.59264464159528e-07</v>
+        <v>1.30664996357417e-07</v>
       </c>
       <c r="O9" t="n">
         <v>1.396066089140404e-07</v>

--- a/Results/Phase 2/Hydrogen/hydrogen human toxicity non-carcinogenic results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen human toxicity non-carcinogenic results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.203522758417708e-08</v>
+        <v>3.2035227584177e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>3.057942668875757e-08</v>
+        <v>3.05794266887575e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>3.097437303438115e-08</v>
+        <v>3.097437303438114e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.224164956689888e-08</v>
+        <v>2.224164956689884e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>3.083449101090279e-08</v>
+        <v>3.083449101090273e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.227832898757167e-08</v>
+        <v>3.22783289875716e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.078961172940451e-08</v>
+        <v>3.078961172940461e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>3.07573320218154e-08</v>
+        <v>3.075733202181538e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.174859305934646e-08</v>
+        <v>3.174859305934639e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.090946242492484e-08</v>
+        <v>3.090946242492477e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.274262430953041e-08</v>
+        <v>3.274262430953037e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>3.40466854616764e-08</v>
+        <v>3.404668546167638e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.083596516043006e-08</v>
+        <v>3.083596516043e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>3.126734537022103e-08</v>
+        <v>3.126734537022095e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>3.148387232424813e-08</v>
+        <v>3.148387232424809e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.090166671104309e-08</v>
+        <v>3.090166671104303e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>3.070465970510793e-08</v>
+        <v>3.070465970510787e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>3.181170025526366e-08</v>
+        <v>3.18117002552636e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>3.083496255173023e-08</v>
+        <v>3.083496255173014e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>3.348578848962541e-08</v>
+        <v>3.348578848962537e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>2.42361371466091e-08</v>
+        <v>2.423613714660906e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>3.119518662859253e-08</v>
+        <v>3.119518662859246e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.149842751122342e-08</v>
+        <v>3.149842751122328e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.165642175519967e-08</v>
+        <v>3.165642175519959e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.131577307071428e-08</v>
+        <v>3.131577307071419e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.120532536984931e-08</v>
+        <v>3.120532536984923e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.559952617133897e-08</v>
+        <v>3.559952617133891e-08</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.187150198259081e-08</v>
+        <v>2.187150198259076e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.056917956291461e-08</v>
+        <v>3.056917956291453e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="V3" t="n">
         <v>2.361996039406424e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.062794627045776e-08</v>
+        <v>3.062794627045768e-08</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.382733274137394e-07</v>
+        <v>5.382733274137383e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.540133381272244e-07</v>
+        <v>1.540133381272243e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.738939160118148e-07</v>
+        <v>2.738939160118155e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.728737445110629e-07</v>
+        <v>1.728737445110628e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.368188052114711e-07</v>
+        <v>2.368188052114708e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>6.164620375725997e-07</v>
+        <v>6.164620375725992e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>2.264628700063e-07</v>
+        <v>2.264628700062998e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0968683625121e-07</v>
+        <v>2.096868362512099e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.983302402904739e-07</v>
+        <v>4.983302402904738e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.52588609079661e-07</v>
+        <v>2.525886090796605e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>7.725455475504602e-07</v>
+        <v>7.725455475504481e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.222148442037205e-06</v>
+        <v>1.222148442037206e-06</v>
       </c>
       <c r="N4" t="n">
         <v>2.272530204171204e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>3.299428355345565e-07</v>
+        <v>3.299428355345578e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>3.918779949895875e-07</v>
+        <v>3.91877994989587e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.484326442014275e-07</v>
+        <v>2.484326442014267e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.953909981886492e-07</v>
+        <v>1.953909981886486e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>4.891535587933311e-07</v>
+        <v>4.891535587933298e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.321864337952803e-07</v>
+        <v>2.321864337952804e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>9.710017086865703e-07</v>
+        <v>9.710017086865695e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>3.007189607808396e-07</v>
+        <v>3.007189607808386e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.283063643762813e-07</v>
+        <v>3.283063643762808e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>4.293343609114645e-07</v>
+        <v>4.293343609114642e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.64139411397762e-07</v>
+        <v>4.641394113977622e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.496173135385175e-07</v>
+        <v>3.496173135385184e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.327259192073907e-07</v>
+        <v>3.327259192073901e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.761291171821158e-06</v>
+        <v>1.761291171821157e-06</v>
       </c>
     </row>
     <row r="5">
@@ -850,82 +850,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.619559329958086e-07</v>
+        <v>1.619559329958087e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.606124384030893e-07</v>
+        <v>2.60612438403089e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.606124384030893e-07</v>
+        <v>2.60612438403089e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>2.080807594556266e-07</v>
+        <v>2.080807594556269e-07</v>
       </c>
       <c r="F5" t="n">
         <v>1.773254635169268e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.810695074877039e-07</v>
+        <v>2.81069507487704e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.606124384030893e-07</v>
+        <v>2.60612438403089e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.606124384030893e-07</v>
+        <v>2.60612438403089e-07</v>
       </c>
       <c r="J5" t="n">
         <v>2.605535713154065e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.606124384030893e-07</v>
+        <v>2.60612438403089e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.606124384030893e-07</v>
+        <v>2.60612438403089e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.606124384030902e-07</v>
+        <v>2.606124384030899e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.272530204171204e-07</v>
+        <v>1.841371418422399e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>2.051532173685856e-07</v>
+        <v>2.051532173685855e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>2.000016694366796e-07</v>
+        <v>2.0000166943668e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.425676779545175e-07</v>
+        <v>1.425676779545172e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.606124384030893e-07</v>
+        <v>2.60612438403089e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.606124384030893e-07</v>
+        <v>2.60612438403089e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.606124384030893e-07</v>
+        <v>2.60612438403089e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>2.124561554142976e-07</v>
+        <v>2.124561554142977e-07</v>
       </c>
       <c r="V5" t="n">
         <v>2.333406099222306e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>2.606318272475294e-07</v>
+        <v>2.606318272475295e-07</v>
       </c>
       <c r="X5" t="n">
         <v>1.516097427173616e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.586986091048914e-07</v>
+        <v>3.586986091048915e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.601233377562312e-07</v>
+        <v>1.601233377562314e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.606124384030893e-07</v>
+        <v>2.60612438403089e-07</v>
       </c>
       <c r="AB5" t="n">
         <v>3.636674078372615e-07</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.382618089365423e-07</v>
+        <v>1.382618089365422e-07</v>
       </c>
       <c r="C6" t="n">
         <v>1.746496716537631e-07</v>
@@ -947,13 +947,13 @@
         <v>1.746496716537631e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.662515028343201e-07</v>
+        <v>1.662515028343197e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>9.076571440223071e-08</v>
+        <v>9.076571440223054e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.746496735678239e-07</v>
+        <v>1.746496735678236e-07</v>
       </c>
       <c r="H6" t="n">
         <v>1.746496716537631e-07</v>
@@ -962,7 +962,7 @@
         <v>1.746496716537631e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.745908045660807e-07</v>
+        <v>1.745908045660803e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.746496716537631e-07</v>
@@ -974,16 +974,16 @@
         <v>1.746496716537631e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>2.272530204171204e-07</v>
+        <v>1.746496716537631e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.867085642607923e-07</v>
+        <v>1.86708564260792e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>1.893311660907889e-07</v>
+        <v>1.893311660907885e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.746496735678239e-07</v>
+        <v>1.746496735678236e-07</v>
       </c>
       <c r="R6" t="n">
         <v>1.746496716537631e-07</v>
@@ -998,7 +998,7 @@
         <v>1.746496716537631e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>2.163366395834383e-07</v>
+        <v>2.163366395834382e-07</v>
       </c>
       <c r="W6" t="n">
         <v>1.746496716537631e-07</v>
@@ -1010,7 +1010,7 @@
         <v>1.746496716537631e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.527110269303338e-07</v>
+        <v>1.527110269303336e-07</v>
       </c>
       <c r="AA6" t="n">
         <v>1.746496716537631e-07</v>
@@ -1029,82 +1029,82 @@
         <v>2.091843034558962e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.959626891524575e-08</v>
+        <v>2.959626891524573e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.728420738820506e-08</v>
+        <v>2.728420738820496e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.881696199572528e-08</v>
+        <v>1.881696199572523e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.81166101229173e-08</v>
+        <v>2.811661012291719e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.947846987549662e-08</v>
+        <v>1.947846987549653e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.838272917941852e-08</v>
+        <v>2.838272917941831e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.855968108489377e-08</v>
+        <v>2.855968108489361e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.225685086517776e-08</v>
+        <v>2.225685086517763e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.766002691202983e-08</v>
+        <v>2.766002691202972e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.679824993003516e-08</v>
+        <v>1.679824993003521e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>9.369569917180271e-09</v>
+        <v>9.36956991718019e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.808361696600999e-08</v>
+        <v>2.808361696600988e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.548093155304445e-08</v>
+        <v>2.548093155304438e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.418553548142853e-08</v>
+        <v>2.418553548142838e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.770225050249035e-08</v>
+        <v>2.770225050249026e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.887158521619814e-08</v>
+        <v>2.887158521619806e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.227454999986146e-08</v>
+        <v>2.227454999986143e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.810250887351203e-08</v>
+        <v>2.810250887351198e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.23864495785731e-08</v>
+        <v>1.2386449578573e-08</v>
       </c>
       <c r="V7" t="n">
         <v>1.92579157688104e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>2.595449606038918e-08</v>
+        <v>2.595449606038912e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.420821703985089e-08</v>
+        <v>2.420821703985087e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.324447361824361e-08</v>
+        <v>2.324447361824349e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.520477174238791e-08</v>
+        <v>2.520477174238793e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.589864338343166e-08</v>
+        <v>2.589864338343157e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.99140175711984e-10</v>
+        <v>1.991401757119227e-10</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.761736689597074e-08</v>
+        <v>2.761736689597067e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.011001020437545e-08</v>
+        <v>3.011001020437533e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.945296118709263e-08</v>
+        <v>2.945296118709244e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.085182413863369e-08</v>
+        <v>2.085182413863355e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.969182506061841e-08</v>
+        <v>2.969182506061829e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.720528169659128e-08</v>
+        <v>2.720528169659122e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.976803079789931e-08</v>
+        <v>2.976803079789925e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.98162647712137e-08</v>
+        <v>2.981626477121377e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.796645701205636e-08</v>
+        <v>2.796645701205614e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.955904965864234e-08</v>
+        <v>2.955904965864225e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.645006840201089e-08</v>
+        <v>2.645006840201091e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.437405647450939e-08</v>
+        <v>2.437405647450934e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.967828721860995e-08</v>
+        <v>2.967828721860978e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.89254372712353e-08</v>
+        <v>2.892543727123511e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.855255488449479e-08</v>
+        <v>2.855255488449478e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.957046581297869e-08</v>
+        <v>2.957046581297862e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>2.990550982822923e-08</v>
+        <v>2.99055098282291e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>2.801087833144793e-08</v>
+        <v>2.801087833144791e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.968588048802848e-08</v>
+        <v>2.968588048802841e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.518584936261715e-08</v>
+        <v>2.5185849362617e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.225139294110719e-08</v>
+        <v>2.225139294110716e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>2.90687518896092e-08</v>
+        <v>2.90687518896091e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.857743025283411e-08</v>
+        <v>2.85774302528341e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.8296918168711e-08</v>
+        <v>2.829691816871083e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.884821137781072e-08</v>
+        <v>2.884821137781056e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.905347748485839e-08</v>
+        <v>2.90534774848583e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.175432242737828e-08</v>
+        <v>2.175432242737822e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.963706307510796e-08</v>
+        <v>2.963706307510798e-08</v>
       </c>
       <c r="C2" t="n">
         <v>2.962195857546641e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.973481485979002e-08</v>
+        <v>2.973481485979003e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.124092170945768e-08</v>
+        <v>2.124092170945765e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.965334715210558e-08</v>
+        <v>2.965334715210559e-08</v>
       </c>
       <c r="G2" t="n">
         <v>2.983465911116504e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.972959223966252e-08</v>
+        <v>2.972959223966248e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.972659058409376e-08</v>
+        <v>2.972659058409377e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.975215372407151e-08</v>
+        <v>2.975215372407149e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.97530838025025e-08</v>
+        <v>2.975308380250251e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.974429334084419e-08</v>
+        <v>2.974429334084417e-08</v>
       </c>
       <c r="M2" t="n">
         <v>2.979564325039242e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.970031513751588e-08</v>
+        <v>2.970031513751585e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.964208671436912e-08</v>
+        <v>2.964208671436913e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>2.96837505992432e-08</v>
+        <v>2.968375059924318e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.967969527865314e-08</v>
+        <v>2.967969527865315e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>2.97383237775257e-08</v>
+        <v>2.973832377752567e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>2.974509343655287e-08</v>
+        <v>2.974509343655285e-08</v>
       </c>
       <c r="T2" t="n">
         <v>2.969250450298526e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.986893168518818e-08</v>
+        <v>2.986893168518816e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>2.308774697342486e-08</v>
+        <v>2.308774697342476e-08</v>
       </c>
       <c r="W2" t="n">
         <v>2.997947287355704e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.05768999942013e-08</v>
+        <v>3.057689999420128e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.050830027792346e-08</v>
+        <v>3.050830027792342e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.968016734760522e-08</v>
+        <v>2.968016734760527e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.991039576857494e-08</v>
+        <v>2.991039576857492e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.978143591120828e-08</v>
+        <v>2.978143591120827e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.125853663051383e-08</v>
+        <v>2.12585366305138e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.966364378975028e-08</v>
+        <v>2.966364378975029e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.289580559250629e-08</v>
+        <v>2.289580559250618e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.969097214886126e-08</v>
+        <v>2.969097214886127e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.969097214914947e-08</v>
+        <v>2.969097214914948e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.256543646281745e-07</v>
+        <v>1.256543646281746e-07</v>
       </c>
       <c r="C4" t="n">
         <v>1.329529962328068e-07</v>
@@ -1543,13 +1543,13 @@
         <v>1.605018607300534e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>5.974767521831193e-08</v>
+        <v>5.974767521831194e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.396842274573527e-07</v>
+        <v>1.396842274573524e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.746323527173664e-07</v>
+        <v>1.74632352717366e-07</v>
       </c>
       <c r="H4" t="n">
         <v>1.627616690742491e-07</v>
@@ -1558,16 +1558,16 @@
         <v>1.577536183805913e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.646817542261892e-07</v>
+        <v>1.646817542261891e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>1.681721568094672e-07</v>
+        <v>1.681721568094669e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>1.583905898173758e-07</v>
+        <v>1.583905898173759e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.789519797390426e-07</v>
+        <v>1.789519797390425e-07</v>
       </c>
       <c r="N4" t="n">
         <v>1.447088091876592e-07</v>
@@ -1576,43 +1576,43 @@
         <v>1.298148214193616e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>1.364361545687156e-07</v>
+        <v>1.364361545687155e-07</v>
       </c>
       <c r="Q4" t="n">
         <v>1.419007770195771e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.611682630775172e-07</v>
+        <v>1.611682630775169e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.524009418509541e-07</v>
+        <v>1.524009418509539e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.466886049534904e-07</v>
+        <v>1.466886049534902e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>1.859602532923421e-07</v>
+        <v>1.859602532923417e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.623946669308372e-07</v>
+        <v>1.623946669308371e-07</v>
       </c>
       <c r="W4" t="n">
         <v>2.134538431589678e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>3.624677639230097e-07</v>
+        <v>3.624677639230099e-07</v>
       </c>
       <c r="Y4" t="n">
         <v>3.506780521749335e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.377414832405742e-07</v>
+        <v>1.377414832405741e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.966392056583148e-07</v>
+        <v>1.966392056583147e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.772920741935324e-07</v>
+        <v>1.772920741935326e-07</v>
       </c>
     </row>
     <row r="5">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.399285538673215e-07</v>
+        <v>1.399285538673212e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.249802134192716e-07</v>
+        <v>2.249802134192718e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.249802134192716e-07</v>
+        <v>2.249802134192718e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.796927135722644e-07</v>
+        <v>1.796927135722643e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.531786084071856e-07</v>
+        <v>1.531786084071855e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.426162290883402e-07</v>
+        <v>2.426162290883399e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.249802134192716e-07</v>
+        <v>2.249802134192718e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.249802134192716e-07</v>
+        <v>2.249802134192718e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.249284105514185e-07</v>
+        <v>2.249284105514182e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.249802134192716e-07</v>
+        <v>2.249802134192718e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.249802134192716e-07</v>
+        <v>2.249802134192718e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.249802134192711e-07</v>
+        <v>2.249802134192709e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.447088091876592e-07</v>
+        <v>1.590509484370162e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.771688829150354e-07</v>
+        <v>1.771688829150357e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.727277393830768e-07</v>
+        <v>1.727277393830765e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.232139615525036e-07</v>
+        <v>1.232139615525039e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.249802134192716e-07</v>
+        <v>2.249802134192718e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.249802134192716e-07</v>
+        <v>2.249802134192718e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.249802134192716e-07</v>
+        <v>2.249802134192718e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83472430405441e-07</v>
+        <v>1.834724304054408e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>2.014809149573841e-07</v>
+        <v>2.01480914957384e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>2.249969285200302e-07</v>
+        <v>2.249969285200296e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.310091151584544e-07</v>
+        <v>1.310091151584548e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.095533486020454e-07</v>
+        <v>3.095533486020453e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.383486756243943e-07</v>
+        <v>1.383486756243942e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.249802134192716e-07</v>
+        <v>2.249802134192718e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.13823783737294e-07</v>
+        <v>3.138237837372942e-07</v>
       </c>
     </row>
     <row r="6">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.652311199646858e-08</v>
+        <v>9.652311199646849e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="E6" t="n">
         <v>1.157647843887033e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>6.387165484664847e-08</v>
+        <v>6.387165484664837e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.215381540632092e-07</v>
+        <v>1.215381540632091e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.214863425305779e-07</v>
+        <v>1.214863425305778e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.447088091876592e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.298281062497299e-07</v>
+        <v>1.298281062497298e-07</v>
       </c>
       <c r="P6" t="n">
         <v>1.316310286186682e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.215381540632092e-07</v>
+        <v>1.215381540632091e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>1.501462606264099e-07</v>
+        <v>1.501462606264097e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.064563081212966e-07</v>
+        <v>1.064563081212965e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.215381453984315e-07</v>
+        <v>1.215381453984312e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1798,82 +1798,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.871939685561727e-08</v>
+        <v>2.871939685561725e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.882389139891103e-08</v>
+        <v>2.882389139891104e-08</v>
       </c>
       <c r="D7" t="n">
         <v>2.816398989518404e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.051227681169294e-08</v>
+        <v>2.051227681169289e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.864702993185502e-08</v>
+        <v>2.864702993185504e-08</v>
       </c>
       <c r="G7" t="n">
         <v>2.75451473906532e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.820569382215542e-08</v>
+        <v>2.820569382215541e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.821520051988613e-08</v>
+        <v>2.821520051988614e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.785334371661551e-08</v>
+        <v>2.785334371661547e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.805446843840931e-08</v>
+        <v>2.805446843840932e-08</v>
       </c>
       <c r="L7" t="n">
         <v>2.809246433986325e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.781537591003203e-08</v>
+        <v>2.781537591003206e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.835986819602938e-08</v>
+        <v>2.835986819602939e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.868825575635057e-08</v>
+        <v>2.86882557563506e-08</v>
       </c>
       <c r="P7" t="n">
         <v>2.843889057631709e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.848340191268393e-08</v>
+        <v>2.848340191268392e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.815010461659982e-08</v>
+        <v>2.81501046165998e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.80821322868286e-08</v>
+        <v>2.808213228682859e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.841273151394412e-08</v>
+        <v>2.84127315139441e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.73531512190203e-08</v>
+        <v>2.735315121902033e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.108760082585108e-08</v>
+        <v>2.108760082585094e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>2.670733913930975e-08</v>
+        <v>2.670733913930974e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.32250813114311e-08</v>
+        <v>2.322508131143118e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.359630307987222e-08</v>
+        <v>2.35963030798722e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.846448905157456e-08</v>
+        <v>2.846448905157457e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.711726248327255e-08</v>
+        <v>2.711726248327256e-08</v>
       </c>
       <c r="AB7" t="n">
         <v>2.789127358103602e-08</v>
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.919499322032408e-08</v>
+        <v>2.919499322032406e-08</v>
       </c>
       <c r="C8" t="n">
         <v>2.922743407088553e-08</v>
@@ -1895,7 +1895,7 @@
         <v>2.904003306803203e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.090137111370522e-08</v>
+        <v>2.09013711137052e-08</v>
       </c>
       <c r="F8" t="n">
         <v>2.917835011639014e-08</v>
@@ -1904,19 +1904,19 @@
         <v>2.885830200771145e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9053785867579e-08</v>
+        <v>2.905378586757898e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.905510978977381e-08</v>
+        <v>2.905510978977383e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.892846142171117e-08</v>
+        <v>2.892846142171115e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.900846939888786e-08</v>
+        <v>2.900846939888784e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.901696719347684e-08</v>
+        <v>2.901696719347682e-08</v>
       </c>
       <c r="M8" t="n">
         <v>2.894224098442342e-08</v>
@@ -1925,19 +1925,19 @@
         <v>2.90946585968696e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.918584756017807e-08</v>
+        <v>2.918584756017811e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.911404949345719e-08</v>
+        <v>2.911404949345722e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.913024697276328e-08</v>
+        <v>2.913024697276331e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>2.903722413976214e-08</v>
+        <v>2.90372241397621e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>2.901306617212841e-08</v>
+        <v>2.901306617212843e-08</v>
       </c>
       <c r="T8" t="n">
         <v>2.911090094045562e-08</v>
@@ -1946,25 +1946,25 @@
         <v>2.880521571178617e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.226500804219002e-08</v>
+        <v>2.226500804218995e-08</v>
       </c>
       <c r="W8" t="n">
         <v>2.862191034580573e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.763489905746795e-08</v>
+        <v>2.763489905746796e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.773520642897551e-08</v>
+        <v>2.773520642897549e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.912211362963891e-08</v>
+        <v>2.912211362963892e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.873934966867489e-08</v>
+        <v>2.873934966867485e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.896256732741761e-08</v>
+        <v>2.896256732741762e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.165273187517944e-08</v>
+        <v>3.165273187517975e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>3.041700002298302e-08</v>
+        <v>3.041700002298305e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>3.11982938208946e-08</v>
+        <v>3.119829382089467e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.212221529586312e-08</v>
+        <v>2.212221529586323e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>3.066874202794135e-08</v>
+        <v>3.066874202794141e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.211798070354328e-08</v>
+        <v>3.211798070354333e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05213855351741e-08</v>
+        <v>3.052138553517412e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>3.056169818233379e-08</v>
+        <v>3.056169818233386e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.162783734655625e-08</v>
+        <v>3.162783734655633e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.074310164998139e-08</v>
+        <v>3.074310164998145e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.261016192355341e-08</v>
+        <v>3.261016192355366e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>3.369276546818531e-08</v>
+        <v>3.369276546818534e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.070245362026604e-08</v>
+        <v>3.070245362026609e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>3.105573844400815e-08</v>
+        <v>3.105573844400823e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>3.15895035904913e-08</v>
+        <v>3.158950359049137e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.074497520744728e-08</v>
+        <v>3.074497520744736e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>3.053752871864446e-08</v>
+        <v>3.053752871864452e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>3.169904115288173e-08</v>
+        <v>3.169904115288175e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>3.071760228201373e-08</v>
+        <v>3.071760228201381e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>3.306005779699697e-08</v>
+        <v>3.306005779699701e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>2.375967932806241e-08</v>
+        <v>2.375967932806245e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>3.098618976816172e-08</v>
+        <v>3.098618976816179e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.14862067426178e-08</v>
+        <v>3.148620674261797e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.142357445904588e-08</v>
+        <v>3.142357445904592e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.106045249148355e-08</v>
+        <v>3.106045249148373e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.088775890609626e-08</v>
+        <v>3.088775890609635e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.533092969794843e-08</v>
+        <v>3.533092969794847e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.181688988534422e-08</v>
+        <v>2.181688988534429e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.043827237776529e-08</v>
+        <v>3.043827237776535e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.339126376936238e-08</v>
+        <v>2.339126376936246e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.050567241476878e-08</v>
+        <v>3.050567241476886e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.05056724149293e-08</v>
+        <v>3.050567241492938e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.364691497122041e-07</v>
+        <v>4.364691497122073e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.361327624041727e-07</v>
+        <v>1.361327624041729e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>3.548223569159112e-07</v>
+        <v>3.548223569159104e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.445559177202059e-07</v>
+        <v>1.445559177202344e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.084040096598391e-07</v>
+        <v>2.084040096598395e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>5.635222058286574e-07</v>
+        <v>5.635222058286596e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.691051059816842e-07</v>
+        <v>1.691051059816851e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.750598120297317e-07</v>
+        <v>1.750598120297323e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.692386944625551e-07</v>
+        <v>4.692386944625519e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.257859099296845e-07</v>
+        <v>2.257859099296872e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>7.201177334924156e-07</v>
+        <v>7.20117733492532e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.072192895049694e-06</v>
+        <v>1.072192895049692e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.094846361198606e-07</v>
+        <v>2.094846361198624e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.861000443150292e-07</v>
+        <v>2.861000443150297e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>4.246048013037886e-07</v>
+        <v>4.246048013037954e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.225794691753116e-07</v>
+        <v>2.225794691753229e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.697255566631751e-07</v>
+        <v>1.697255566631753e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>4.573151835256287e-07</v>
+        <v>4.573151835256386e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.188341421698727e-07</v>
+        <v>2.188341421698807e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>8.267279887483109e-07</v>
+        <v>8.267279887483111e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>2.190508719900684e-07</v>
+        <v>2.190508719900685e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>2.835710718618929e-07</v>
+        <v>2.835710718618927e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>4.313171959274516e-07</v>
+        <v>4.31317195927468e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.022831205058074e-07</v>
+        <v>4.022831205058075e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.91767804981107e-07</v>
+        <v>2.917678049811122e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.57689149545357e-07</v>
+        <v>2.576891495453665e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.605655738125025e-06</v>
+        <v>1.605655738125032e-06</v>
       </c>
     </row>
     <row r="5">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.517973746558021e-07</v>
+        <v>1.517973746558017e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.441602293071668e-07</v>
+        <v>2.441602293071663e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.441602293071668e-07</v>
+        <v>2.441602293071663e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.949797337363506e-07</v>
+        <v>1.949797337363503e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.66186427944489e-07</v>
+        <v>1.661864279444886e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.633122689081639e-07</v>
+        <v>2.633122689081631e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.441602293071668e-07</v>
+        <v>2.441602293071663e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.441602293071668e-07</v>
+        <v>2.441602293071663e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.44099610032557e-07</v>
+        <v>2.440996100325563e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.441602293071668e-07</v>
+        <v>2.441602293071663e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.441602293071668e-07</v>
+        <v>2.441602293071663e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.441602293071683e-07</v>
+        <v>2.441602293071675e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.094846361198605e-07</v>
+        <v>1.725635649867412e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.92238950012445e-07</v>
+        <v>1.922389500124446e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.874160377179304e-07</v>
+        <v>1.874160377179302e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.336459656338877e-07</v>
+        <v>1.336459656338873e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.441602293071668e-07</v>
+        <v>2.441602293071662e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.441602293071668e-07</v>
+        <v>2.441602293071663e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.441602293071668e-07</v>
+        <v>2.441602293071661e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.99073965740148e-07</v>
+        <v>1.990739657401474e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>2.185953490820932e-07</v>
+        <v>2.185953490820927e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>2.441783812679153e-07</v>
+        <v>2.441783812679145e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.421112047986733e-07</v>
+        <v>1.421112047986728e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.359856399748885e-07</v>
+        <v>3.359856399748876e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.500816872102718e-07</v>
+        <v>1.500816872102717e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.441602293071668e-07</v>
+        <v>2.441602293071663e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.406409542593478e-07</v>
+        <v>3.406409542593473e-07</v>
       </c>
     </row>
     <row r="6">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.204274337246167e-07</v>
+        <v>1.204274337246168e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.446771650832656e-07</v>
+        <v>1.446771650832658e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>7.927773279367856e-08</v>
+        <v>7.927773279367855e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.519531783521245e-07</v>
+        <v>1.519531783521247e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.518925566348945e-07</v>
+        <v>1.518925566348946e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>2.094846361198606e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.624007688422458e-07</v>
+        <v>1.624007688422459e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>1.646729405233786e-07</v>
+        <v>1.646729405233787e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.519531783521245e-07</v>
+        <v>1.519531783521247e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>1.880181780347774e-07</v>
+        <v>1.880181780347777e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="Z6" t="n">
         <v>1.329459577203303e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.519531759095045e-07</v>
+        <v>1.519531759095043e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.23483287686129e-08</v>
+        <v>2.234832876861249e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.971347297758353e-08</v>
+        <v>2.971347297758362e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.513809163024891e-08</v>
+        <v>2.513809163024903e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.914333879596981e-08</v>
+        <v>1.914333879596941e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.825173493040708e-08</v>
+        <v>2.825173493040714e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.958664655750618e-08</v>
+        <v>1.958664655750623e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.911358740002532e-08</v>
+        <v>2.911358740002539e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.887030781889604e-08</v>
+        <v>2.88703078188961e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.207677342627772e-08</v>
+        <v>2.207677342627776e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.780036954344009e-08</v>
+        <v>2.780036954344018e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.674025062554365e-08</v>
+        <v>1.674025062554161e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06030101429346e-08</v>
+        <v>1.060301014293469e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.803146790637486e-08</v>
+        <v>2.803146790637495e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.589476616151832e-08</v>
+        <v>2.58947661615184e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.270880784973875e-08</v>
+        <v>2.27088078497388e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.778610905677618e-08</v>
+        <v>2.778610905677619e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.901501629152568e-08</v>
+        <v>2.901501629152576e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.209930760067713e-08</v>
+        <v>2.209930760067675e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.795547335837858e-08</v>
+        <v>2.795547335837843e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.406400037500628e-08</v>
+        <v>1.406400037500632e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.051223200342925e-08</v>
+        <v>2.051223200342931e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>2.634809401351088e-08</v>
+        <v>2.634809401351091e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.344469154440513e-08</v>
+        <v>2.34446915444049e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.377777582712183e-08</v>
+        <v>2.377777582712191e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.587720192590438e-08</v>
+        <v>2.58772019259043e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.69320763899294e-08</v>
+        <v>2.693207638992937e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.377629738507454e-10</v>
+        <v>9.377629738508348e-10</v>
       </c>
     </row>
     <row r="8">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.794111452019373e-08</v>
+        <v>2.794111452019384e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.00565467544009e-08</v>
+        <v>3.005654675440095e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.875602745840002e-08</v>
+        <v>2.875602745840007e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.090574103009598e-08</v>
+        <v>2.090574103009593e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.964319328961118e-08</v>
+        <v>2.964319328961121e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.714978914154499e-08</v>
+        <v>2.714978914154505e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.988798241708108e-08</v>
+        <v>2.988798241708111e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.98176020795409e-08</v>
+        <v>2.981760207954095e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.782332867711327e-08</v>
+        <v>2.782332867711332e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.951218022216511e-08</v>
+        <v>2.951218022216515e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.634685114158655e-08</v>
+        <v>2.634685114158664e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.463699070840638e-08</v>
+        <v>2.463699070840646e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.957668268405183e-08</v>
+        <v>2.957668268405189e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.895776140461976e-08</v>
+        <v>2.895776140461984e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.80419053661965e-08</v>
+        <v>2.804190536619657e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.950756521275343e-08</v>
+        <v>2.950756521275347e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>2.985927543205662e-08</v>
+        <v>2.985927543205664e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>2.787411837290186e-08</v>
+        <v>2.787411837290185e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.955725358428097e-08</v>
+        <v>2.955725358428099e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.557904462233207e-08</v>
+        <v>2.557904462233213e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.244971069963299e-08</v>
+        <v>2.244971069963303e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>2.909447834610011e-08</v>
+        <v>2.909447834610013e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.82734379445184e-08</v>
+        <v>2.827343794451831e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.836236007113225e-08</v>
+        <v>2.836236007113231e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.895448366891695e-08</v>
+        <v>2.89544836689171e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.926176132634649e-08</v>
+        <v>2.926176132634659e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.187743667492118e-08</v>
+        <v>2.187743667492121e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.15917784544465e-08</v>
+        <v>3.159177845444653e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>3.061080349765866e-08</v>
+        <v>3.061080349765867e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>3.153110772414388e-08</v>
+        <v>3.153110772414392e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.213533454400645e-08</v>
+        <v>2.213533454400648e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>3.094632791653201e-08</v>
+        <v>3.094632791653203e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.219022080218785e-08</v>
+        <v>3.219022080218786e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.068264192731374e-08</v>
+        <v>3.068264192731377e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>3.105473199010883e-08</v>
+        <v>3.105473199010884e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.17716266866742e-08</v>
+        <v>3.177162668667421e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.115459573985994e-08</v>
+        <v>3.115459573985996e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.252620072534261e-08</v>
+        <v>3.252620072534263e-08</v>
       </c>
       <c r="M2" t="n">
         <v>3.346119743842221e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.081873326737547e-08</v>
+        <v>3.081873326737548e-08</v>
       </c>
       <c r="O2" t="n">
         <v>3.111505232282697e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>3.175289410889136e-08</v>
+        <v>3.175289410889137e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.093957318124663e-08</v>
+        <v>3.093957318124665e-08</v>
       </c>
       <c r="R2" t="n">
         <v>3.067936321471181e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>3.178708852111017e-08</v>
+        <v>3.178708852111019e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>3.090194283047444e-08</v>
+        <v>3.090194283047445e-08</v>
       </c>
       <c r="U2" t="n">
         <v>3.257603548734943e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>2.426136263580685e-08</v>
+        <v>2.426136263580689e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>3.116648136535992e-08</v>
+        <v>3.116648136535995e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.204015751475241e-08</v>
+        <v>3.204015751475243e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.250644301224247e-08</v>
+        <v>3.250644301224248e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.125375315891097e-08</v>
+        <v>3.125375315891098e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.106395654159918e-08</v>
+        <v>3.10639565415992e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.515597718766979e-08</v>
+        <v>3.515597718766984e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3014,7 +3014,7 @@
         <v>3.068101690340171e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.062368103007639e-08</v>
+        <v>3.06236810300764e-08</v>
       </c>
       <c r="K3" t="n">
         <v>3.068101690340171e-08</v>
@@ -3050,7 +3050,7 @@
         <v>3.068101690340171e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.37125643670802e-08</v>
+        <v>2.371256436708019e-08</v>
       </c>
       <c r="W3" t="n">
         <v>3.068101690340171e-08</v>
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.556208299845435e-07</v>
+        <v>3.556208299845442e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.356522402288988e-07</v>
+        <v>1.356522402288989e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>3.718394761606568e-07</v>
+        <v>3.718394761606571e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.246565379934402e-07</v>
+        <v>1.2465653799344e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.212878473031126e-07</v>
+        <v>2.212878473031128e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.963729026325314e-07</v>
+        <v>4.963729026325318e-07</v>
       </c>
       <c r="H4" t="n">
         <v>1.540146082665841e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.492014581030226e-07</v>
+        <v>2.492014581030224e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.269536235320989e-07</v>
+        <v>4.269536235320992e-07</v>
       </c>
       <c r="K4" t="n">
         <v>2.666529603990968e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.04520291277306e-07</v>
+        <v>6.045202912773055e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>8.929516533249902e-07</v>
+        <v>8.929516533249901e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.809472060526751e-07</v>
+        <v>1.809472060526753e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.408047781923305e-07</v>
+        <v>2.408047781923311e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>3.910895005323758e-07</v>
+        <v>3.910895005323766e-07</v>
       </c>
       <c r="Q4" t="n">
         <v>2.122570951802511e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.50024968521078e-07</v>
+        <v>1.500249685210781e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>4.039085320039786e-07</v>
+        <v>4.03908532003979e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.071654445289574e-07</v>
+        <v>2.071654445289578e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>6.039184680569432e-07</v>
+        <v>6.039184680569428e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>2.455599262857957e-07</v>
+        <v>2.455599262858e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>2.664407818820199e-07</v>
+        <v>2.664407818820197e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>4.996603357220035e-07</v>
+        <v>4.996603357220039e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.039109080950298e-07</v>
+        <v>6.039109080950314e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.704274108918828e-07</v>
+        <v>2.704274108918826e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.412864671357789e-07</v>
+        <v>2.41286467135779e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.404527526661841e-06</v>
+        <v>1.404527526661843e-06</v>
       </c>
     </row>
     <row r="5">
@@ -3166,7 +3166,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.424792365849669e-07</v>
+        <v>1.42479236584967e-07</v>
       </c>
       <c r="C5" t="n">
         <v>2.288178658417663e-07</v>
@@ -3175,13 +3175,13 @@
         <v>2.288178658417663e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.828450925902311e-07</v>
+        <v>1.82845092590231e-07</v>
       </c>
       <c r="F5" t="n">
         <v>1.559297859636755e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.467207430629464e-07</v>
+        <v>2.467207430629469e-07</v>
       </c>
       <c r="H5" t="n">
         <v>2.288178658417663e-07</v>
@@ -3190,7 +3190,7 @@
         <v>2.288178658417663e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.287594484633313e-07</v>
+        <v>2.287594484633312e-07</v>
       </c>
       <c r="K5" t="n">
         <v>2.288178658417663e-07</v>
@@ -3199,19 +3199,19 @@
         <v>2.288178658417664e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.288178658417682e-07</v>
+        <v>2.288178658417684e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.809472060526751e-07</v>
+        <v>1.618909840328252e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.802830722768013e-07</v>
+        <v>1.802830722768014e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.757747270323455e-07</v>
+        <v>1.757747270323456e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.25511725349595e-07</v>
+        <v>1.255117253495951e-07</v>
       </c>
       <c r="R5" t="n">
         <v>2.288178658417663e-07</v>
@@ -3223,28 +3223,28 @@
         <v>2.288178658417663e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.866757265032924e-07</v>
+        <v>1.866757265032925e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>2.049177339333269e-07</v>
+        <v>2.04917733933327e-07</v>
       </c>
       <c r="W5" t="n">
         <v>2.288348338686037e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.334248322860297e-07</v>
+        <v>1.334248322860299e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.146599931736311e-07</v>
+        <v>3.146599931736314e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.408754522190735e-07</v>
+        <v>1.408754522190736e-07</v>
       </c>
       <c r="AA5" t="n">
         <v>2.288178658417663e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.190057836308531e-07</v>
+        <v>3.190057836308532e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3266,7 +3266,7 @@
         <v>1.285217121810143e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>7.084209546194462e-08</v>
+        <v>7.084209546194466e-08</v>
       </c>
       <c r="G6" t="n">
         <v>1.349388574359197e-07</v>
@@ -3284,19 +3284,19 @@
         <v>1.349388539645701e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.349388539645701e-07</v>
+        <v>1.349388539645702e-07</v>
       </c>
       <c r="M6" t="n">
         <v>1.349388539645701e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.809472060526751e-07</v>
+        <v>1.349388539645701e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.441532037079133e-07</v>
+        <v>1.441532037079132e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>1.461571659305105e-07</v>
+        <v>1.461571659305104e-07</v>
       </c>
       <c r="Q6" t="n">
         <v>1.349388574359197e-07</v>
@@ -3314,13 +3314,13 @@
         <v>1.349388539645701e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>1.667235909304649e-07</v>
+        <v>1.66723590930465e-07</v>
       </c>
       <c r="W6" t="n">
         <v>1.349388539645701e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.349388539645701e-07</v>
+        <v>1.349388539645702e-07</v>
       </c>
       <c r="Y6" t="n">
         <v>1.349388539645701e-07</v>
@@ -3342,46 +3342,46 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.392097407203412e-08</v>
+        <v>2.392097407203414e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.977221197294793e-08</v>
+        <v>2.977221197294795e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.438270769930365e-08</v>
+        <v>2.438270769930367e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.944525225569454e-08</v>
+        <v>1.944525225569456e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.782281376394646e-08</v>
+        <v>2.782281376394645e-08</v>
       </c>
       <c r="G7" t="n">
         <v>2.036656423729541e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.936260654852422e-08</v>
+        <v>2.93626065485242e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.717992971191459e-08</v>
+        <v>2.717992971191457e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.250636612177688e-08</v>
+        <v>2.250636612177687e-08</v>
       </c>
       <c r="K7" t="n">
         <v>2.658214104374891e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.844014516926947e-08</v>
+        <v>1.844014516926946e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.314449747700032e-08</v>
+        <v>1.314449747700033e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.85458687414407e-08</v>
+        <v>2.854586874144073e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.675266291314732e-08</v>
+        <v>2.675266291314733e-08</v>
       </c>
       <c r="P7" t="n">
         <v>2.294691615447053e-08</v>
@@ -3396,31 +3396,31 @@
         <v>2.278394399612982e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.806981551307273e-08</v>
+        <v>2.806981551307275e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.813287502575992e-08</v>
+        <v>1.813287502575993e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.974301829580148e-08</v>
+        <v>1.974301829580139e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>2.648583136153822e-08</v>
+        <v>2.648583136153823e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.139184972568541e-08</v>
+        <v>2.139184972568539e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.859718933090144e-08</v>
+        <v>1.859718933090145e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.593737326942669e-08</v>
+        <v>2.59373732694267e-08</v>
       </c>
       <c r="AA7" t="n">
         <v>2.709398709140698e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.156169727391927e-09</v>
+        <v>3.156169727391892e-09</v>
       </c>
     </row>
     <row r="8">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.851593742319598e-08</v>
+        <v>2.851593742319601e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.019729435811273e-08</v>
+        <v>3.019729435811276e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.866535696475879e-08</v>
+        <v>2.866535696475881e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.103143405053897e-08</v>
+        <v>2.103143405053901e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.96458363795269e-08</v>
+        <v>2.964583637952693e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.749711196889915e-08</v>
+        <v>2.749711196889917e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.008276101431999e-08</v>
+        <v>3.008276101431998e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.94617261606793e-08</v>
+        <v>2.946172616067933e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.80782225350501e-08</v>
+        <v>2.807822253505015e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.928959416137559e-08</v>
+        <v>2.928959416137561e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.695656507696881e-08</v>
+        <v>2.695656507696883e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.548202521383809e-08</v>
+        <v>2.54820252138381e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.984723404936974e-08</v>
+        <v>2.984723404936977e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.932763873833985e-08</v>
+        <v>2.932763873833987e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.823385362101103e-08</v>
+        <v>2.823385362101102e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.964691038253478e-08</v>
+        <v>2.964691038253481e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>3.008628598114362e-08</v>
+        <v>3.008628598114364e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>2.819389518182336e-08</v>
+        <v>2.819389518182337e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.971383787646965e-08</v>
+        <v>2.971383787646969e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.686659094446696e-08</v>
+        <v>2.686659094446697e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.245520652318229e-08</v>
+        <v>2.245520652318227e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>2.925765857454896e-08</v>
+        <v>2.925765857454899e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.781355684607215e-08</v>
+        <v>2.781355684607218e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.700826295795596e-08</v>
+        <v>2.700826295795597e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.909538018835703e-08</v>
+        <v>2.909538018835705e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.943184654595583e-08</v>
+        <v>2.943184654595586e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.263208400610197e-08</v>
+        <v>2.263208400610202e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.160010575781616e-08</v>
+        <v>3.160010575781611e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>3.078666031485912e-08</v>
+        <v>3.078666031485921e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>3.150040969199746e-08</v>
+        <v>3.150040969199751e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.204157386019148e-08</v>
+        <v>2.204157386019141e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>3.117884196775366e-08</v>
+        <v>3.117884196775377e-08</v>
       </c>
       <c r="G2" t="n">
         <v>3.215546163800784e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.086203487734685e-08</v>
+        <v>3.086203487734687e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>3.121240425437221e-08</v>
+        <v>3.121240425437226e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.186107141045612e-08</v>
+        <v>3.186107141045606e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.140300282051522e-08</v>
+        <v>3.140300282051526e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.234350504327622e-08</v>
+        <v>3.234350504327615e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>3.316248190837184e-08</v>
+        <v>3.316248190837187e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.09284281708825e-08</v>
+        <v>3.092842817088261e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>3.109193082997969e-08</v>
+        <v>3.109193082997984e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>3.181388587385269e-08</v>
+        <v>3.181388587385277e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.113174068088722e-08</v>
+        <v>3.113174068088724e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>3.093940887498236e-08</v>
+        <v>3.093940887498247e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>3.185204385271436e-08</v>
+        <v>3.185204385271452e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>3.112447561556938e-08</v>
+        <v>3.112447561556949e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>3.276082254870874e-08</v>
+        <v>3.276082254870882e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>2.509912711780048e-08</v>
+        <v>2.509912711780049e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>3.137101509059427e-08</v>
+        <v>3.137101509059437e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.235054798483314e-08</v>
+        <v>3.23505479848333e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.377088596138186e-08</v>
+        <v>3.377088596138179e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.137189002950942e-08</v>
+        <v>3.137189002950941e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.128882932842722e-08</v>
+        <v>3.128882932842738e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.488551964799255e-08</v>
+        <v>3.488551964799257e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.187021982545252e-08</v>
+        <v>2.18702198254526e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.080871439208777e-08</v>
+        <v>3.080871439208776e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.416848276695159e-08</v>
+        <v>2.416848276695157e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.08433235857477e-08</v>
+        <v>3.084332358574773e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.084332358603591e-08</v>
+        <v>3.084332358603594e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3853,49 +3853,49 @@
         <v>3.150217145295068e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.40004999414445e-07</v>
+        <v>1.400049994144452e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>3.174657018505528e-07</v>
+        <v>3.174657018505534e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.044225040387988e-07</v>
+        <v>1.044225040387989e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>2.393947034673765e-07</v>
+        <v>2.393947034673766e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.420654214185971e-07</v>
+        <v>4.420654214185935e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.590545471948362e-07</v>
+        <v>1.590545471948366e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>2.481434333894647e-07</v>
+        <v>2.481434333894648e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>3.982165679280337e-07</v>
+        <v>3.982165679280349e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.868676893589903e-07</v>
+        <v>2.86867689358991e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>5.060846312383889e-07</v>
+        <v>5.060846312383898e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>7.460946142505622e-07</v>
+        <v>7.460946142505623e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.679578788102533e-07</v>
+        <v>1.679578788102534e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.996529128099227e-07</v>
+        <v>1.996529128099229e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>3.613808460250959e-07</v>
+        <v>3.613808460250953e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.188238230504012e-07</v>
+        <v>2.188238230504013e-07</v>
       </c>
       <c r="R4" t="n">
         <v>1.771567665513522e-07</v>
@@ -3904,28 +3904,28 @@
         <v>3.782945315451669e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>2.237213315390765e-07</v>
+        <v>2.237213315390767e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>5.946881865033854e-07</v>
+        <v>5.946881865033846e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>3.305486747699077e-07</v>
+        <v>3.3054867476991e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>2.778359344677978e-07</v>
+        <v>2.778359344677979e-07</v>
       </c>
       <c r="X4" t="n">
         <v>5.267320179154396e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.9545123397608e-07</v>
+        <v>8.954512339760784e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.558296340780657e-07</v>
+        <v>2.558296340780659e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.579460061881149e-07</v>
+        <v>2.579460061881151e-07</v>
       </c>
       <c r="AB4" t="n">
         <v>1.267309747061437e-06</v>
@@ -3938,85 +3938,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.430610248747978e-07</v>
+        <v>1.430610248747977e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.295512977388404e-07</v>
+        <v>2.295512977388402e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.295512977388404e-07</v>
+        <v>2.295512977388402e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.834977787396626e-07</v>
+        <v>1.83497778739663e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.565351985552099e-07</v>
+        <v>1.5653519855521e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.47485619249842e-07</v>
+        <v>2.474856192498423e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.295512977388404e-07</v>
+        <v>2.295512977388402e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.295512977388404e-07</v>
+        <v>2.295512977388402e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.294977067206328e-07</v>
+        <v>2.29497706720633e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.295512977388404e-07</v>
+        <v>2.295512977388402e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.295512977388404e-07</v>
+        <v>2.295512977388403e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.295512977388439e-07</v>
+        <v>2.295512977388438e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.679578788102533e-07</v>
+        <v>1.625068667648456e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.809312585400107e-07</v>
+        <v>1.809312585400108e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.764149949195007e-07</v>
+        <v>1.764149949195008e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.260637122095185e-07</v>
+        <v>1.260637122095188e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.295512977388404e-07</v>
+        <v>2.295512977388402e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.295512977388404e-07</v>
+        <v>2.295512977388402e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.295512977388404e-07</v>
+        <v>2.295512977388402e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.873430825822753e-07</v>
+        <v>1.873430825822754e-07</v>
       </c>
       <c r="V5" t="n">
         <v>2.056493523701042e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>2.295682955679329e-07</v>
+        <v>2.295682955679328e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.339907175838432e-07</v>
+        <v>1.339907175838434e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.155577828657935e-07</v>
+        <v>3.155577828657934e-07</v>
       </c>
       <c r="Z5" t="n">
         <v>1.414544236510487e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.295512977388404e-07</v>
+        <v>2.295512977388402e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.198976199558772e-07</v>
+        <v>3.198976199558769e-07</v>
       </c>
     </row>
     <row r="6">
@@ -4029,82 +4029,82 @@
         <v>1.02904401277808e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.23318832014333e-07</v>
+        <v>1.233188320143329e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>6.826287444770705e-08</v>
+        <v>6.826287444770721e-08</v>
       </c>
       <c r="G6" t="n">
         <v>1.29444082093121e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.293904870558437e-07</v>
+        <v>1.293904870558436e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.679578788102533e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.382392975645747e-07</v>
+        <v>1.382392975645748e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>1.401521060291281e-07</v>
+        <v>1.40152106029128e-07</v>
       </c>
       <c r="Q6" t="n">
         <v>1.29444082093121e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>1.59800219016736e-07</v>
+        <v>1.598002190167362e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.134430145619869e-07</v>
+        <v>1.134430145619867e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.294440780740511e-07</v>
+        <v>1.29444078074051e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.499309885309177e-08</v>
+        <v>2.49930988530919e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.984891260402309e-08</v>
+        <v>2.984891260402306e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.566940898505872e-08</v>
+        <v>2.566940898505869e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.000038622160054e-08</v>
+        <v>2.000038622160062e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.75697784491221e-08</v>
+        <v>2.756977844912213e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.16943695979706e-08</v>
+        <v>2.169436959797083e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.941940927705134e-08</v>
+        <v>2.941940927705136e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.736320664330993e-08</v>
+        <v>2.736320664331003e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.32566351508134e-08</v>
+        <v>2.325663515081333e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.623325167550073e-08</v>
+        <v>2.623325167550066e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.063585721772952e-08</v>
+        <v>2.063585721772951e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.599089479215403e-08</v>
+        <v>1.599089479215405e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.901149199661067e-08</v>
+        <v>2.901149199661078e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.801307651046403e-08</v>
+        <v>2.801307651046415e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.370691104476589e-08</v>
+        <v>2.370691104476591e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.782081625221763e-08</v>
+        <v>2.78208162522176e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.896350038296772e-08</v>
+        <v>2.89635003829678e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.351740980289137e-08</v>
+        <v>2.351740980289133e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.787343716077829e-08</v>
+        <v>2.787343716077819e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.815594942427808e-08</v>
+        <v>1.815594942427812e-08</v>
       </c>
       <c r="V7" t="n">
         <v>1.790395222090163e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>2.639273226962189e-08</v>
+        <v>2.639273226962191e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.067977394933836e-08</v>
+        <v>2.067977394933844e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.225904644849438e-08</v>
+        <v>1.225904644849436e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.63559376675997e-08</v>
+        <v>2.635593766759973e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.688115244698973e-08</v>
+        <v>2.688115244698968e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.84669189043856e-09</v>
+        <v>5.846691890438602e-09</v>
       </c>
     </row>
     <row r="8">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.893823486076634e-08</v>
+        <v>2.893823486076654e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.03342001490436e-08</v>
+        <v>3.033420014904358e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.914626206026531e-08</v>
+        <v>2.914626206026537e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.119079361163272e-08</v>
+        <v>2.119079361163263e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.968936849828854e-08</v>
+        <v>2.968936849828862e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.799265841745164e-08</v>
+        <v>2.799265841745179e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>3.021414932901319e-08</v>
+        <v>3.02141493290132e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.962893995495724e-08</v>
+        <v>2.962893995495728e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.842485128862771e-08</v>
+        <v>2.842485128862764e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.930540540979415e-08</v>
+        <v>2.930540540979419e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.769907531643157e-08</v>
+        <v>2.76990753164315e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.640457947527339e-08</v>
+        <v>2.640457947527344e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.009493895999337e-08</v>
+        <v>3.009493895999326e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.980415939113241e-08</v>
+        <v>2.980415939113243e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.856679542517745e-08</v>
+        <v>2.856679542517751e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.975649021184063e-08</v>
+        <v>2.975649021184052e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>3.008408332694531e-08</v>
+        <v>3.008408332694534e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>2.851872973508167e-08</v>
+        <v>2.851872973508174e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.977316782761061e-08</v>
+        <v>2.977316782761072e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.698802687284651e-08</v>
+        <v>2.698802687284658e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.224874575547345e-08</v>
+        <v>2.224874575547344e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>2.934598185843293e-08</v>
+        <v>2.9345981858433e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.772610051082509e-08</v>
+        <v>2.772610051082507e-08</v>
       </c>
       <c r="Y8" t="n">
         <v>2.531498063935428e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.933011513617056e-08</v>
+        <v>2.933011513617053e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.948602883347118e-08</v>
+        <v>2.94860288334711e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.351197256695702e-08</v>
+        <v>2.351197256695709e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4446,82 +4446,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.964867125079703e-08</v>
+        <v>2.964867125079705e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.946630372268431e-08</v>
+        <v>2.94663037226843e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.966807923533237e-08</v>
+        <v>2.966807923533238e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.123582655301696e-08</v>
+        <v>2.123582655301699e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.954435887878272e-08</v>
+        <v>2.954435887878274e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.997279972875794e-08</v>
+        <v>2.997279972875792e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.971841726751073e-08</v>
+        <v>2.971841726751069e-08</v>
       </c>
       <c r="I2" t="n">
         <v>2.956328804875247e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.982294916346364e-08</v>
+        <v>2.982294916346369e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.967686779623577e-08</v>
+        <v>2.967686779623573e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.010421726228031e-08</v>
+        <v>3.010421726228028e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>3.053198386530021e-08</v>
+        <v>3.05319838653002e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.963251000916834e-08</v>
+        <v>2.963251000916832e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.958184239466547e-08</v>
+        <v>2.958184239466546e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>2.979166849432431e-08</v>
+        <v>2.979166849432426e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.961649225975069e-08</v>
+        <v>2.961649225975067e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>2.960820646121882e-08</v>
+        <v>2.960820646121883e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>2.976240381957557e-08</v>
+        <v>2.976240381957556e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>2.957570873720221e-08</v>
+        <v>2.957570873720217e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>3.037769203306969e-08</v>
+        <v>3.03776920330697e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>2.271916091775326e-08</v>
+        <v>2.271916091775319e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.990913279019143e-08</v>
+        <v>2.990913279019147e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>2.982753533810287e-08</v>
+        <v>2.982753533810286e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.964234814925897e-08</v>
+        <v>2.964234814925895e-08</v>
       </c>
       <c r="Z2" t="n">
         <v>2.973711379782642e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.97232876468751e-08</v>
+        <v>2.972328764687511e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>3.060162613241399e-08</v>
@@ -4534,85 +4534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.121169637869161e-08</v>
+        <v>2.121169637869163e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.954093305518089e-08</v>
+        <v>2.954093305518084e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.260439459342908e-08</v>
+        <v>2.260439459342902e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.95804327078278e-08</v>
+        <v>2.958043270782778e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.958043270798832e-08</v>
+        <v>2.95804327079883e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4625,82 +4625,82 @@
         <v>1.645083081530844e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.266683707143276e-07</v>
+        <v>1.266683707143271e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.805911166026844e-07</v>
+        <v>1.80591116602685e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.740668257004825e-08</v>
+        <v>6.740668257004808e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.494591599018318e-07</v>
+        <v>1.494591599018317e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.461325269612704e-07</v>
+        <v>2.461325269612705e-07</v>
       </c>
       <c r="H4" t="n">
         <v>2.020269903813968e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.52180744318853e-07</v>
+        <v>1.521807443188531e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.224178434124457e-07</v>
+        <v>2.224178434124458e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>1.873428009465929e-07</v>
+        <v>1.87342800946593e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.829169757631909e-07</v>
+        <v>2.829169757631907e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>4.105651086664787e-07</v>
+        <v>4.105651086664784e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.665714283592557e-07</v>
+        <v>1.665714283592554e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.513430924822645e-07</v>
+        <v>1.513430924822649e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>1.983472657799052e-07</v>
+        <v>1.98347265779905e-07</v>
       </c>
       <c r="Q4" t="n">
         <v>1.638811040157464e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.654139924247368e-07</v>
+        <v>1.654139924247365e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.936265912748625e-07</v>
+        <v>1.936265912748626e-07</v>
       </c>
       <c r="T4" t="n">
         <v>1.592093863085941e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>3.55934161065485e-07</v>
+        <v>3.559341610654848e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.547502675709072e-07</v>
+        <v>1.547502675709067e-07</v>
       </c>
       <c r="W4" t="n">
         <v>2.392764120262133e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>2.23081866483686e-07</v>
+        <v>2.230818664836875e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.695519384444217e-07</v>
+        <v>1.695519384444208e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.864220865259152e-07</v>
+        <v>1.864220865259151e-07</v>
       </c>
       <c r="AA4" t="n">
         <v>1.897837248129433e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.554073694742819e-07</v>
+        <v>4.554073694742811e-07</v>
       </c>
     </row>
     <row r="5">
@@ -4713,82 +4713,82 @@
         <v>1.490902754521527e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.399884517097642e-07</v>
+        <v>2.399884517097639e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.399884517097642e-07</v>
+        <v>2.399884517097639e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.915878541782706e-07</v>
+        <v>1.915878541782707e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.632511489651734e-07</v>
+        <v>1.632511489651733e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.588367807043317e-07</v>
+        <v>2.588367807043315e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.399884517097642e-07</v>
+        <v>2.399884517097639e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.399884517097642e-07</v>
+        <v>2.399884517097639e-07</v>
       </c>
       <c r="J5" t="n">
         <v>2.399339141996461e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.399884517097642e-07</v>
+        <v>2.399884517097639e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.399884517097642e-07</v>
+        <v>2.399884517097639e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.399884517097641e-07</v>
+        <v>2.399884517097639e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.665714283592557e-07</v>
+        <v>1.695271581799078e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.888905334542079e-07</v>
+        <v>1.888905334542076e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.841441022889616e-07</v>
+        <v>1.841441022889613e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.312267091642058e-07</v>
+        <v>1.312267091642055e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.399884517097642e-07</v>
+        <v>2.399884517097639e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.399884517097642e-07</v>
+        <v>2.399884517097639e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.399884517097642e-07</v>
+        <v>2.399884517097639e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.956250137560546e-07</v>
+        <v>1.956250137560544e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>2.148714502421152e-07</v>
+        <v>2.148714502421151e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>2.400063158194449e-07</v>
+        <v>2.400063158194444e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.395577076439702e-07</v>
+        <v>1.395577076439701e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.303711415567222e-07</v>
+        <v>3.303711415567218e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.474017951597343e-07</v>
+        <v>1.474017951597341e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.399884517097642e-07</v>
+        <v>2.399884517097639e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.349391976054411e-07</v>
+        <v>3.349391976054407e-07</v>
       </c>
     </row>
     <row r="6">
@@ -4810,10 +4810,10 @@
         <v>1.367890739984833e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>7.493113420436898e-08</v>
+        <v>7.493113420436902e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.436710785506532e-07</v>
+        <v>1.436710785506531e-07</v>
       </c>
       <c r="H6" t="n">
         <v>1.436710712604346e-07</v>
@@ -4834,16 +4834,16 @@
         <v>1.436710712604346e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.665714283592557e-07</v>
+        <v>1.436710712604346e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.535529139260708e-07</v>
+        <v>1.53552913926071e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>1.557020435764788e-07</v>
+        <v>1.557020435764789e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.436710785506532e-07</v>
+        <v>1.436710785506531e-07</v>
       </c>
       <c r="R6" t="n">
         <v>1.436710712604346e-07</v>
@@ -4870,7 +4870,7 @@
         <v>1.436710712604346e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.25693131826455e-07</v>
+        <v>1.256931318264551e-07</v>
       </c>
       <c r="AA6" t="n">
         <v>1.436710712604346e-07</v>
@@ -4889,82 +4889,82 @@
         <v>2.78897101536635e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.898534767186891e-08</v>
+        <v>2.898534767186886e-08</v>
       </c>
       <c r="D7" t="n">
         <v>2.780428403064202e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.022003798702993e-08</v>
+        <v>2.022003798702994e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.853482899800659e-08</v>
+        <v>2.853482899800652e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.596351555872151e-08</v>
+        <v>2.596351555872149e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.752441541756998e-08</v>
+        <v>2.752441541756995e-08</v>
       </c>
       <c r="I7" t="n">
         <v>2.842054616780348e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.659072160602697e-08</v>
+        <v>2.659072160602692e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7750019531836e-08</v>
+        <v>2.775001953183597e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.520810475289494e-08</v>
+        <v>2.520810475289491e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.277042319472434e-08</v>
+        <v>2.277042319472432e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.800539887600034e-08</v>
+        <v>2.800539887600031e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.828571426221332e-08</v>
+        <v>2.828571426221328e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.703368433770095e-08</v>
+        <v>2.703368433770097e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.81023133825489e-08</v>
+        <v>2.810231338254886e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.816117837004913e-08</v>
+        <v>2.816117837004919e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.722084757397815e-08</v>
+        <v>2.722084757397808e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.834622660229419e-08</v>
+        <v>2.834622660229414e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.358524688804641e-08</v>
+        <v>2.358524688804644e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.127541198282471e-08</v>
+        <v>2.127541198282465e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>2.636701531307661e-08</v>
+        <v>2.636701531307657e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.686750375716216e-08</v>
+        <v>2.686750375716212e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.794445022927343e-08</v>
+        <v>2.794445022927346e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.736617264021056e-08</v>
+        <v>2.736617264021053e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.746572748388081e-08</v>
+        <v>2.746572748388083e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.233761601618862e-08</v>
+        <v>2.233761601618854e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4974,82 +4974,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.887938710056615e-08</v>
+        <v>2.887938710056617e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.91955381348265e-08</v>
+        <v>2.919553813482649e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.885992592688984e-08</v>
+        <v>2.885992592688981e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.07846188245831e-08</v>
+        <v>2.078461882458313e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.906860585859979e-08</v>
+        <v>2.906860585859974e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.832709089941053e-08</v>
+        <v>2.832709089941052e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.878292284823208e-08</v>
+        <v>2.878292284823209e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.903553597662929e-08</v>
+        <v>2.903553597662928e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.848059355233264e-08</v>
+        <v>2.848059355233261e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.884402396790574e-08</v>
+        <v>2.884402396790578e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.811479410893037e-08</v>
+        <v>2.811479410893038e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.743340783455247e-08</v>
+        <v>2.743340783455245e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.891586459627882e-08</v>
+        <v>2.89158645962788e-08</v>
       </c>
       <c r="O8" t="n">
         <v>2.899274137581497e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.863288986983804e-08</v>
+        <v>2.863288986983803e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.894394325618895e-08</v>
+        <v>2.894394325618898e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>2.896244121456129e-08</v>
+        <v>2.896244121456128e-08</v>
       </c>
       <c r="S8" t="n">
         <v>2.868878506404931e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.901414102592994e-08</v>
+        <v>2.901414102592983e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.764986337947254e-08</v>
+        <v>2.764986337947258e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.211446959471198e-08</v>
+        <v>2.211446959471192e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>2.844701763495299e-08</v>
+        <v>2.8447017634953e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.859314401988541e-08</v>
+        <v>2.859314401988535e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.889797090794994e-08</v>
+        <v>2.889797090794993e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.872961841055939e-08</v>
+        <v>2.87296184105594e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.876109003074055e-08</v>
+        <v>2.876109003074052e-08</v>
       </c>
       <c r="AB8" t="n">
         <v>2.730612145615783e-08</v>
@@ -5218,85 +5218,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.952318274274151e-08</v>
+        <v>2.952318274274146e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.94910336472714e-08</v>
+        <v>2.949103364727137e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.95776430458716e-08</v>
+        <v>2.957764304587158e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.122163198743658e-08</v>
+        <v>2.122163198743655e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.954299221112053e-08</v>
+        <v>2.954299221112048e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.965953415791575e-08</v>
+        <v>2.965953415791571e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.962502728594971e-08</v>
+        <v>2.962502728594969e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.96006466179686e-08</v>
+        <v>2.960064661796856e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.959842565601819e-08</v>
+        <v>2.959842565601813e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.960834789309543e-08</v>
+        <v>2.960834789309542e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.958781140439451e-08</v>
+        <v>2.95878114043945e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>2.958786049328419e-08</v>
+        <v>2.958786049328418e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.961976583292114e-08</v>
+        <v>2.96197658329211e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.960885816386501e-08</v>
+        <v>2.960885816386498e-08</v>
       </c>
       <c r="P2" t="n">
         <v>2.95332043446437e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.952652490793349e-08</v>
+        <v>2.952652490793348e-08</v>
       </c>
       <c r="R2" t="n">
         <v>2.961582749139555e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>2.959786020475083e-08</v>
+        <v>2.959786020475082e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>2.951855201693487e-08</v>
+        <v>2.951855201693484e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.956585492060425e-08</v>
+        <v>2.956585492060423e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>2.285252789899108e-08</v>
+        <v>2.28525278989911e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.973810295769088e-08</v>
+        <v>2.973810295769086e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.018534130473737e-08</v>
+        <v>3.018534130473734e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.989825284020537e-08</v>
+        <v>2.989825284020535e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.964257603417665e-08</v>
+        <v>2.964257603417663e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.970799321513667e-08</v>
+        <v>2.970799321513665e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.954691758426885e-08</v>
+        <v>2.954691758426883e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5306,85 +5306,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.120091589025161e-08</v>
+        <v>2.120091589025158e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.952891205572953e-08</v>
+        <v>2.952891205572954e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.269089110693808e-08</v>
+        <v>2.269089110693797e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.95576999156392e-08</v>
+        <v>2.955769991563917e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.955769991580337e-08</v>
+        <v>2.955769991580334e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.288295012513361e-07</v>
+        <v>1.288295012513364e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.332524950233094e-07</v>
+        <v>1.332524950233093e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.555401993766102e-07</v>
+        <v>1.5554019937661e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.283195910412256e-08</v>
+        <v>6.283195910412242e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.45509832597044e-07</v>
+        <v>1.455098325970438e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.683123586198613e-07</v>
+        <v>1.683123586198618e-07</v>
       </c>
       <c r="H4" t="n">
         <v>1.700603736921628e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.599775041267849e-07</v>
+        <v>1.599775041267845e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.61170060707475e-07</v>
+        <v>1.611700607074756e-07</v>
       </c>
       <c r="K4" t="n">
         <v>1.65200180956767e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>1.612252132384731e-07</v>
+        <v>1.612252132384727e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.676706598668153e-07</v>
+        <v>1.676706598668152e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5786046225733e-07</v>
+        <v>1.578604622573298e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.522510956497655e-07</v>
+        <v>1.522510956497657e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>1.30608864895266e-07</v>
+        <v>1.306088648952662e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.386764539589936e-07</v>
+        <v>1.386764539589935e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.647542722929189e-07</v>
+        <v>1.647542722929187e-07</v>
       </c>
       <c r="S4" t="n">
         <v>1.507130759603678e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.420841983305327e-07</v>
+        <v>1.420841983305325e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>1.51887970081896e-07</v>
+        <v>1.518879700818959e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.565295835279736e-07</v>
+        <v>1.565295835279758e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>1.87562655435856e-07</v>
+        <v>1.875626554358555e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>2.978771158540407e-07</v>
+        <v>2.978771158540412e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.278227812029769e-07</v>
+        <v>2.278227812029766e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.578553876628069e-07</v>
+        <v>1.578553876628067e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.790005790136158e-07</v>
+        <v>1.790005790136163e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.506611647458692e-07</v>
+        <v>1.506611647458691e-07</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.393906895691837e-07</v>
+        <v>1.393906895691833e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.241204781328858e-07</v>
+        <v>2.24120478132885e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.241204781328858e-07</v>
+        <v>2.24120478132885e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.790043650925449e-07</v>
+        <v>1.790043650925442e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.525906003708532e-07</v>
+        <v>1.525906003708526e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.41689751755739e-07</v>
+        <v>2.41689751755738e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.241204781328858e-07</v>
+        <v>2.24120478132885e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.241204781328858e-07</v>
+        <v>2.24120478132885e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.240682873858696e-07</v>
+        <v>2.240682873858687e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.241204781328858e-07</v>
+        <v>2.24120478132885e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.241204781328858e-07</v>
+        <v>2.24120478132885e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.241204781328857e-07</v>
+        <v>2.241204781328848e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5786046225733e-07</v>
+        <v>1.584407170143391e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.764900856641475e-07</v>
+        <v>1.764900856641467e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.720657492734716e-07</v>
+        <v>1.72065749273471e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.227393522499368e-07</v>
+        <v>1.227393522499363e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.241204781328858e-07</v>
+        <v>2.24120478132885e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.241204781328858e-07</v>
+        <v>2.24120478132885e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.241204781328858e-07</v>
+        <v>2.24120478132885e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8277012009078e-07</v>
+        <v>1.827701200907794e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>2.007070034251351e-07</v>
+        <v>2.007070034251344e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>2.241371299766607e-07</v>
+        <v>2.2413712997666e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.305050057401782e-07</v>
+        <v>1.305050057401778e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.083741386536718e-07</v>
+        <v>3.083741386536708e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.378167902451244e-07</v>
+        <v>1.378167902451238e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.241204781328858e-07</v>
+        <v>2.24120478132885e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.126278272891595e-07</v>
+        <v>3.126278272891586e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5570,85 +5570,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.003655060362627e-07</v>
+        <v>1.003655060362625e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.204312169032647e-07</v>
+        <v>1.204312169032644e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>6.631572672399286e-08</v>
+        <v>6.631572672399274e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.264518352910771e-07</v>
+        <v>1.26451835291077e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.263996352232497e-07</v>
+        <v>1.263996352232492e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5786046225733e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.350968106489946e-07</v>
+        <v>1.350968106489942e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3697694446654e-07</v>
+        <v>1.369769444665398e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.264518352910771e-07</v>
+        <v>1.26451835291077e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>1.562936782101382e-07</v>
+        <v>1.56293678210138e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="Z6" t="n">
         <v>1.107240984373295e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.264518259702658e-07</v>
+        <v>1.264518259702657e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5658,85 +5658,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.847926158267952e-08</v>
+        <v>2.847926158267949e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.868523507887469e-08</v>
+        <v>2.868523507887467e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.817908175700898e-08</v>
+        <v>2.817908175700894e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.022957047988399e-08</v>
+        <v>2.022957047988397e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.838850461182777e-08</v>
+        <v>2.838850461182774e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.766922383610319e-08</v>
+        <v>2.766922383610327e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.791371674179792e-08</v>
+        <v>2.791371674179789e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.804743893579278e-08</v>
+        <v>2.804743893579276e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.783604579804677e-08</v>
+        <v>2.783604579804678e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.79968236858089e-08</v>
+        <v>2.799682368580889e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.810485342989475e-08</v>
+        <v>2.810485342989471e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.812523485451872e-08</v>
+        <v>2.812523485451868e-08</v>
       </c>
       <c r="N7" t="n">
         <v>2.792487022465597e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.79676702395844e-08</v>
+        <v>2.796767023958437e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.841710737420562e-08</v>
+        <v>2.841710737420559e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.847537466446772e-08</v>
+        <v>2.84753746644677e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.796229915238849e-08</v>
+        <v>2.796229915238845e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.804013646742774e-08</v>
+        <v>2.804013646742773e-08</v>
       </c>
       <c r="T7" t="n">
         <v>2.852596007556615e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.823319597320884e-08</v>
+        <v>2.823319597320882e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.107738376902921e-08</v>
+        <v>2.107738376902912e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>2.722049191032923e-08</v>
+        <v>2.722049191032919e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.461456537920011e-08</v>
+        <v>2.46145653792001e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.628082375458976e-08</v>
+        <v>2.628082375458973e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.777111829700934e-08</v>
+        <v>2.777111829700932e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.740009239789336e-08</v>
+        <v>2.740009239789333e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.835928761669323e-08</v>
+        <v>2.835928761669321e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.90324898643911e-08</v>
+        <v>2.903248986439108e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.90940593660884e-08</v>
+        <v>2.909405936608838e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.895036739022476e-08</v>
+        <v>2.895036739022472e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.077966673022515e-08</v>
+        <v>2.077966673022513e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.901100462180727e-08</v>
+        <v>2.901100462180724e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.880027152343595e-08</v>
+        <v>2.8800271523436e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.887700970271369e-08</v>
+        <v>2.887700970271366e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.891347305914762e-08</v>
+        <v>2.891347305914758e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.882816611392785e-08</v>
+        <v>2.88281661139278e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.889814423423054e-08</v>
+        <v>2.889814423423052e-08</v>
       </c>
       <c r="L8" t="n">
         <v>2.892676162335905e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.893608432540442e-08</v>
+        <v>2.893608432540441e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.887682311992964e-08</v>
+        <v>2.887682311992958e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.888538959406147e-08</v>
+        <v>2.888538959406145e-08</v>
       </c>
       <c r="P8" t="n">
         <v>2.901423110336396e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.903406346940985e-08</v>
+        <v>2.903406346940983e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>2.888991505980123e-08</v>
+        <v>2.888991505980119e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>2.890736399955218e-08</v>
+        <v>2.890736399955215e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.904910710166716e-08</v>
+        <v>2.904910710166715e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.89632014057801e-08</v>
+        <v>2.896320140578006e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.211837691829974e-08</v>
+        <v>2.211837691829979e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>2.867466586696017e-08</v>
+        <v>2.867466586696016e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.79361993377478e-08</v>
+        <v>2.793619933774776e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.840726374414315e-08</v>
+        <v>2.840726374414314e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.882967570412756e-08</v>
+        <v>2.882967570412755e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.872627491860044e-08</v>
+        <v>2.87262749186004e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.900163616906036e-08</v>
+        <v>2.900163616906032e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5990,85 +5990,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.968742400339999e-08</v>
+        <v>2.968742400339995e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.961790449738898e-08</v>
+        <v>2.961790449738893e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.973320723630349e-08</v>
+        <v>2.973320723630344e-08</v>
       </c>
       <c r="E2" t="n">
         <v>2.1384225503342e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.966037880470191e-08</v>
+        <v>2.966037880470188e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.985190599858498e-08</v>
+        <v>2.985190599858494e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.97275005971703e-08</v>
+        <v>2.972750059717028e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.972795539878858e-08</v>
+        <v>2.972795539878854e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.974643639059892e-08</v>
+        <v>2.974643639059891e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.974958674905025e-08</v>
+        <v>2.974958674905022e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.971359739351853e-08</v>
+        <v>2.971359739351852e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>2.974429278593423e-08</v>
+        <v>2.97442927859342e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.970637972288671e-08</v>
+        <v>2.970637972288667e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>2.975078606437631e-08</v>
+        <v>2.975078606437629e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>2.969263114582839e-08</v>
+        <v>2.969263114582837e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.966233116565431e-08</v>
+        <v>2.966233116565427e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>2.978494120599262e-08</v>
+        <v>2.978494120599258e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>2.969144219645309e-08</v>
+        <v>2.969144219645306e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>2.966658111141804e-08</v>
+        <v>2.966658111141802e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>2.969024391484858e-08</v>
+        <v>2.969024391484857e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>2.306126301494077e-08</v>
+        <v>2.306126301494079e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>3.002165269406079e-08</v>
+        <v>3.002165269406076e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.049746652195087e-08</v>
+        <v>3.049746652195084e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.003348831390093e-08</v>
+        <v>3.00334883139009e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.971422135302282e-08</v>
+        <v>2.971422135302279e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.988450273324175e-08</v>
+        <v>2.988450273324173e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.972939773065064e-08</v>
+        <v>2.97293977306506e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6078,85 +6078,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.130244559035416e-08</v>
+        <v>2.130244559035414e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.965908544763477e-08</v>
+        <v>2.965908544763475e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.286852315635848e-08</v>
+        <v>2.28685231563585e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.968744501953889e-08</v>
+        <v>2.968744501953888e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.968744501982709e-08</v>
+        <v>2.968744501982708e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6175,22 +6175,22 @@
         <v>1.605780651586763e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>8.238094924060786e-08</v>
+        <v>8.238094924060784e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.420187241916747e-07</v>
+        <v>1.420187241916749e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.793535242701378e-07</v>
+        <v>1.793535242701381e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.636846887204837e-07</v>
+        <v>1.636846887204839e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.587983688727692e-07</v>
+        <v>1.587983688727691e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.644622266797804e-07</v>
+        <v>1.64462226679781e-07</v>
       </c>
       <c r="K4" t="n">
         <v>1.654200229025539e-07</v>
@@ -6199,25 +6199,25 @@
         <v>1.559848606561159e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.683702681019811e-07</v>
+        <v>1.683702681019813e-07</v>
       </c>
       <c r="N4" t="n">
         <v>1.474424641565742e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.547157580600693e-07</v>
+        <v>1.547157580600692e-07</v>
       </c>
       <c r="P4" t="n">
         <v>1.393133162813696e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.38758329174478e-07</v>
+        <v>1.387583291744781e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.747603153480967e-07</v>
+        <v>1.747603153480966e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.412899306238164e-07</v>
+        <v>1.412899306238166e-07</v>
       </c>
       <c r="T4" t="n">
         <v>1.434937743712113e-07</v>
@@ -6226,22 +6226,22 @@
         <v>1.480107527138952e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.622290672694202e-07</v>
+        <v>1.622290672694205e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>2.244465263991309e-07</v>
+        <v>2.244465263991311e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>3.393797540977948e-07</v>
+        <v>3.393797540977951e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.297794096948713e-07</v>
+        <v>2.297794096948719e-07</v>
       </c>
       <c r="Z4" t="n">
         <v>1.457650788469971e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.910519588482925e-07</v>
+        <v>1.910519588482926e-07</v>
       </c>
       <c r="AB4" t="n">
         <v>1.641775727609425e-07</v>
@@ -6257,82 +6257,82 @@
         <v>1.398396372611642e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.248279116202707e-07</v>
+        <v>2.248279116202708e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.248279116202707e-07</v>
+        <v>2.248279116202708e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.795741625187481e-07</v>
+        <v>1.79574162518748e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.530798171287594e-07</v>
+        <v>1.530798171287595e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.424507839566722e-07</v>
+        <v>2.424507839566726e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.248279116202707e-07</v>
+        <v>2.248279116202708e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.248279116202707e-07</v>
+        <v>2.248279116202708e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.247758659423081e-07</v>
+        <v>2.247758659423082e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.248279116202707e-07</v>
+        <v>2.248279116202708e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.248279116202707e-07</v>
+        <v>2.248279116202708e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.248279116202719e-07</v>
+        <v>2.24827911620272e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.474424641565743e-07</v>
+        <v>1.589477807665307e-07</v>
       </c>
       <c r="O5" t="n">
         <v>1.770522127593056e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72614379012756e-07</v>
+        <v>1.726143790127559e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.231375015834918e-07</v>
+        <v>1.23137501583492e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.248279116202707e-07</v>
+        <v>2.248279116202708e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.248279116202707e-07</v>
+        <v>2.248279116202708e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.248279116202707e-07</v>
+        <v>2.248279116202708e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.833524759463047e-07</v>
+        <v>1.833524759463049e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>2.013459418928364e-07</v>
+        <v>2.013459418928367e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>2.248446142638222e-07</v>
+        <v>2.248446142638223e-07</v>
       </c>
       <c r="X5" t="n">
         <v>1.309268458104477e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.093404362315832e-07</v>
+        <v>3.093404362315833e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.382609364307545e-07</v>
+        <v>1.382609364307547e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.248279116202707e-07</v>
+        <v>2.248279116202708e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.136052708039938e-07</v>
+        <v>3.136052708039943e-07</v>
       </c>
     </row>
     <row r="6">
@@ -6342,13 +6342,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.658055435594627e-08</v>
+        <v>9.658055435594621e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="E6" t="n">
         <v>1.158321400075014e-07</v>
@@ -6360,67 +6360,67 @@
         <v>1.216084841069723e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.215564293396322e-07</v>
+        <v>1.21556429339632e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.474424641565742e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.299027072551905e-07</v>
+        <v>1.299027072551904e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>1.317065584850208e-07</v>
+        <v>1.317065584850206e-07</v>
       </c>
       <c r="Q6" t="n">
         <v>1.216084841069723e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="V6" t="n">
         <v>1.502299121137225e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="Z6" t="n">
         <v>1.065188680374533e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.216084750175948e-07</v>
+        <v>1.216084750175947e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6436,76 +6436,76 @@
         <v>2.882447712226216e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.815024067357743e-08</v>
+        <v>2.815024067357742e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.996532562796151e-08</v>
+        <v>1.99653256279615e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.858297271565351e-08</v>
+        <v>2.85829727156535e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.741913755677349e-08</v>
+        <v>2.741913755677343e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.819482959878461e-08</v>
+        <v>2.819482959878458e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.818409188235965e-08</v>
+        <v>2.818409188235963e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.785622037673058e-08</v>
+        <v>2.785622037673055e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.805178780553257e-08</v>
+        <v>2.805178780553256e-08</v>
       </c>
       <c r="L7" t="n">
         <v>2.82505857976674e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.809193002298794e-08</v>
+        <v>2.809193002298792e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.830094537880016e-08</v>
+        <v>2.830094537880014e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.801738535867916e-08</v>
+        <v>2.801738535867915e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.836244144643716e-08</v>
+        <v>2.836244144643715e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.856215667200861e-08</v>
+        <v>2.85621566720086e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.785502897429533e-08</v>
+        <v>2.785502897429532e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.837691571747585e-08</v>
+        <v>2.837691571747586e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.85413287313e-08</v>
+        <v>2.854132873129999e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.838721133825675e-08</v>
+        <v>2.838721133825674e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.105849933120963e-08</v>
+        <v>2.105849933120965e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>2.643507992469089e-08</v>
+        <v>2.643507992469085e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.366762821591322e-08</v>
+        <v>2.36676282159132e-08</v>
       </c>
       <c r="Y7" t="n">
         <v>2.63708231680647e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.823866915178352e-08</v>
+        <v>2.823866915178349e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.724665945723266e-08</v>
+        <v>2.724665945723262e-08</v>
       </c>
       <c r="AB7" t="n">
         <v>2.817285775234239e-08</v>
@@ -6518,85 +6518,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.909995696942488e-08</v>
+        <v>2.909995696942484e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.922525135388142e-08</v>
+        <v>2.922525135388141e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.903377435998031e-08</v>
+        <v>2.903377435998028e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.077583165930486e-08</v>
+        <v>2.077583165930485e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>2.915784038655854e-08</v>
+        <v>2.915784038655851e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.881981887422861e-08</v>
+        <v>2.881981887422858e-08</v>
       </c>
       <c r="H8" t="n">
         <v>2.904835582391287e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.90439249303387e-08</v>
+        <v>2.904392493033868e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.892612703794741e-08</v>
+        <v>2.892612703794739e-08</v>
       </c>
       <c r="K8" t="n">
         <v>2.900535750401597e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.905982186843723e-08</v>
+        <v>2.905982186843721e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.901832837776782e-08</v>
+        <v>2.901832837776779e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.907551796770725e-08</v>
+        <v>2.907551796770723e-08</v>
       </c>
       <c r="O8" t="n">
         <v>2.899090359638964e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.908975029740013e-08</v>
+        <v>2.908975029740011e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.915032138131572e-08</v>
+        <v>2.915032138131571e-08</v>
       </c>
       <c r="R8" t="n">
         <v>2.895118606571221e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>2.909514718747419e-08</v>
+        <v>2.909514718747417e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.914509454768232e-08</v>
+        <v>2.91450945476823e-08</v>
       </c>
       <c r="U8" t="n">
         <v>2.909863344613519e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.223769640629438e-08</v>
+        <v>2.223769640629439e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>2.854181621110124e-08</v>
+        <v>2.854181621110122e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.775843069215218e-08</v>
+        <v>2.775843069215214e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.852441480203346e-08</v>
+        <v>2.852441480203343e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.905502371608823e-08</v>
+        <v>2.90550237160882e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.87739375239392e-08</v>
+        <v>2.877393752393917e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.904025569724186e-08</v>
+        <v>2.904025569724185e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6762,34 +6762,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.087030014826692e-08</v>
+        <v>3.087030014826695e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>3.016820670801357e-08</v>
+        <v>3.016820670801355e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>3.056744124549073e-08</v>
+        <v>3.056744124549074e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.188847454626591e-08</v>
+        <v>2.188847454626596e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>3.032829544659552e-08</v>
+        <v>3.032829544659554e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.180273511655858e-08</v>
+        <v>3.180273511655856e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.029059059102517e-08</v>
+        <v>3.029059059102514e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>3.031428173983447e-08</v>
+        <v>3.031428173983443e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.122057960112491e-08</v>
+        <v>3.122057960112489e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.041936071020497e-08</v>
+        <v>3.04193607102049e-08</v>
       </c>
       <c r="L2" t="n">
         <v>3.21024006255154e-08</v>
@@ -6798,7 +6798,7 @@
         <v>3.334847273438363e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.046591583542631e-08</v>
+        <v>3.046591583542634e-08</v>
       </c>
       <c r="O2" t="n">
         <v>3.04906454524605e-08</v>
@@ -6807,40 +6807,40 @@
         <v>3.104735639065551e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.043673315813642e-08</v>
+        <v>3.043673315813638e-08</v>
       </c>
       <c r="R2" t="n">
         <v>3.033623111378021e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>3.093850681373561e-08</v>
+        <v>3.093850681373556e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>3.037708494621368e-08</v>
+        <v>3.037708494621362e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>3.222497494781363e-08</v>
+        <v>3.22249749478136e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>2.341649724607556e-08</v>
+        <v>2.341649724607558e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>3.065818391518421e-08</v>
+        <v>3.065818391518423e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.122587976350382e-08</v>
+        <v>3.122587976350381e-08</v>
       </c>
       <c r="Y2" t="n">
         <v>3.112499904367121e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.068921028357734e-08</v>
+        <v>3.068921028357735e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.056944667094546e-08</v>
+        <v>3.056944667094544e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.441985529736381e-08</v>
+        <v>3.441985529736376e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6850,85 +6850,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.16675428771334e-08</v>
+        <v>2.166754287713342e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.019485460302795e-08</v>
+        <v>3.019485460302793e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.314276179215506e-08</v>
+        <v>2.314276179215511e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.026157715820047e-08</v>
+        <v>3.026157715820046e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.0261577158361e-08</v>
+        <v>3.026157715836098e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6938,22 +6938,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.004776372517415e-07</v>
+        <v>3.00477637251748e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.343640566836027e-07</v>
+        <v>1.343640566836028e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>2.437847533329773e-07</v>
+        <v>2.437847533329775e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>1.213912283797297e-07</v>
+        <v>1.213912283797318e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>1.802303480130487e-07</v>
+        <v>1.802303480130488e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>5.298427393638226e-07</v>
+        <v>5.298427393638242e-07</v>
       </c>
       <c r="H4" t="n">
         <v>1.722069260897946e-07</v>
@@ -6962,61 +6962,61 @@
         <v>1.742079612698044e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.134482434463375e-07</v>
+        <v>4.1344824344634e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>2.057716337761876e-07</v>
+        <v>2.057716337761879e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>6.319504931068364e-07</v>
+        <v>6.319504931068591e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>9.748346756322816e-07</v>
+        <v>9.748346756322835e-07</v>
       </c>
       <c r="N4" t="n">
         <v>2.106313977908336e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>2.076395411285187e-07</v>
+        <v>2.07639541128519e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>3.472289698782085e-07</v>
+        <v>3.472289698782095e-07</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.032944921795727e-07</v>
+        <v>2.032944921795736e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.812529401356141e-07</v>
+        <v>1.812529401356142e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>3.147629962350078e-07</v>
+        <v>3.147629962350119e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.905913310297249e-07</v>
+        <v>1.905913310297259e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>6.665434571342421e-07</v>
+        <v>6.665434571342442e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.953349031609834e-07</v>
+        <v>1.953349031609838e-07</v>
       </c>
       <c r="W4" t="n">
-        <v>2.598353365221206e-07</v>
+        <v>2.598353365221197e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>4.256290321677225e-07</v>
+        <v>4.256290321677358e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.862399305060218e-07</v>
+        <v>3.86239930506022e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.564066812469144e-07</v>
+        <v>2.564066812469154e-07</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.366552912741131e-07</v>
+        <v>2.36655291274114e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.4005969815186e-06</v>
+        <v>1.400596981518601e-06</v>
       </c>
     </row>
     <row r="5">
@@ -7026,85 +7026,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.510977023282079e-07</v>
+        <v>1.510977023282082e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.430880997091725e-07</v>
+        <v>2.430880997091728e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.430880997091725e-07</v>
+        <v>2.430880997091728e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.941059266480507e-07</v>
+        <v>1.941059266480509e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.654287311271643e-07</v>
+        <v>1.654287311271646e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.621629078688168e-07</v>
+        <v>2.621629078688172e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.430880997091725e-07</v>
+        <v>2.430880997091728e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.430880997091725e-07</v>
+        <v>2.430880997091728e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.43027686906823e-07</v>
+        <v>2.430276869068234e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.430880997091725e-07</v>
+        <v>2.430880997091728e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.430880997091725e-07</v>
+        <v>2.430880997091728e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.430880997091748e-07</v>
+        <v>2.430880997091752e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.106313977908336e-07</v>
+        <v>1.717801520840456e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.913761952549809e-07</v>
+        <v>1.913761952549811e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.865727315662393e-07</v>
+        <v>1.865727315662395e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.330194896608575e-07</v>
+        <v>1.330194896608578e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.430880997091725e-07</v>
+        <v>2.430880997091728e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.430880997091725e-07</v>
+        <v>2.430880997091728e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.430880997091725e-07</v>
+        <v>2.430880997091728e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.981851211148368e-07</v>
+        <v>1.981851211148374e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>2.176279480161723e-07</v>
+        <v>2.176279480161724e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>2.431061784713681e-07</v>
+        <v>2.431061784713687e-07</v>
       </c>
       <c r="X5" t="n">
         <v>1.414505923767114e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.345457396203658e-07</v>
+        <v>3.345457396203663e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.493889334676988e-07</v>
+        <v>1.493889334676991e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.430880997091725e-07</v>
+        <v>2.430880997091728e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.391797618980232e-07</v>
+        <v>3.391797618980234e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7114,85 +7114,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.192950891117791e-07</v>
+        <v>1.192950891117793e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.433280810148927e-07</v>
+        <v>1.433280810148928e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>7.85131763284008e-08</v>
+        <v>7.851317632840088e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.505390626703684e-07</v>
+        <v>1.505390626703685e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.504786479563338e-07</v>
+        <v>1.50478647956334e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>2.106313977908336e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.608932745971977e-07</v>
+        <v>1.608932745971978e-07</v>
       </c>
       <c r="P6" t="n">
-        <v>1.631451380429207e-07</v>
+        <v>1.631451380429208e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.505390626703684e-07</v>
+        <v>1.505390626703685e-07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.505390607586835e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="T6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="U6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>1.862801886888415e-07</v>
+        <v>1.862801886888419e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.317017249370708e-07</v>
+        <v>1.31701724937071e-07</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.505390607586834e-07</v>
+        <v>1.505390607586836e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7202,85 +7202,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.532217343171569e-08</v>
+        <v>2.532217343171568e-08</v>
       </c>
       <c r="C7" t="n">
         <v>2.951199202997716e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.717448535197101e-08</v>
+        <v>2.717448535197097e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.949949702371207e-08</v>
+        <v>1.949949702371218e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.85842384015326e-08</v>
+        <v>2.858423840153258e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.97808760216957e-08</v>
+        <v>1.978087602169563e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.880705405797523e-08</v>
+        <v>2.880705405797524e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.866064752496051e-08</v>
+        <v>2.866064752496047e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.281571485972826e-08</v>
+        <v>2.281571485972823e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.803853008745949e-08</v>
+        <v>2.803853008745943e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.807009290044926e-08</v>
+        <v>1.807009290044915e-08</v>
       </c>
       <c r="M7" t="n">
         <v>1.095858576332266e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.775802715776048e-08</v>
+        <v>2.77580271577605e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.757772122107391e-08</v>
+        <v>2.757772122107386e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.425669639928134e-08</v>
+        <v>2.425669639928131e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.793380099089761e-08</v>
+        <v>2.79338009908976e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.853620629568275e-08</v>
+        <v>2.853620629568268e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.493334755776389e-08</v>
+        <v>2.49333475577638e-08</v>
       </c>
       <c r="T7" t="n">
         <v>2.829085104485726e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.733241825606375e-08</v>
+        <v>1.733241825606368e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>2.084194645596885e-08</v>
+        <v>2.084194645596888e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>2.661439782187511e-08</v>
+        <v>2.661439782187509e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.331082598759092e-08</v>
+        <v>2.331082598759077e-08</v>
       </c>
       <c r="Y7" t="n">
         <v>2.386983802863328e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.64039538873475e-08</v>
+        <v>2.640395388734739e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.714080029500183e-08</v>
+        <v>2.714080029500185e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.614668473552515e-09</v>
+        <v>4.614668473552518e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7290,85 +7290,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.862285571169769e-08</v>
+        <v>2.862285571169758e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.982714308581282e-08</v>
+        <v>2.982714308581281e-08</v>
       </c>
       <c r="D8" t="n">
         <v>2.916280463560544e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.090200677380709e-08</v>
+        <v>2.09020067738071e-08</v>
       </c>
       <c r="F8" t="n">
         <v>2.956510096687716e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.703398269936309e-08</v>
+        <v>2.703398269936306e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.962877794505955e-08</v>
+        <v>2.962877794505953e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>2.958585365477724e-08</v>
+        <v>2.958585365477721e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.78630475020005e-08</v>
+        <v>2.786304750200046e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.940786720851411e-08</v>
+        <v>2.94078672085141e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.655523643621036e-08</v>
+        <v>2.655523643621045e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.456555013465753e-08</v>
+        <v>2.456555013465752e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.932679260681262e-08</v>
+        <v>2.932679260681263e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.926948244805348e-08</v>
+        <v>2.926948244805347e-08</v>
       </c>
       <c r="P8" t="n">
         <v>2.831511650885472e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.93775875837581e-08</v>
+        <v>2.937758758375811e-08</v>
       </c>
       <c r="R8" t="n">
         <v>2.955118187283091e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>2.851414536540366e-08</v>
+        <v>2.851414536540364e-08</v>
       </c>
       <c r="T8" t="n">
         <v>2.948039828423796e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.634216644448371e-08</v>
+        <v>2.634216644448366e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.236961893584742e-08</v>
+        <v>2.23696189358474e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>2.899870569421223e-08</v>
+        <v>2.899870569421217e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.806326583007373e-08</v>
+        <v>2.806326583007371e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.821673737045407e-08</v>
+        <v>2.821673737045412e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.893397940175027e-08</v>
+        <v>2.893397940175028e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.914948325279132e-08</v>
+        <v>2.914948325279126e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.275043011392747e-08</v>
+        <v>2.275043011392744e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
         <v>2.98728678129219e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.987547017159464e-08</v>
+        <v>2.987547017159463e-08</v>
       </c>
       <c r="D2" t="n">
         <v>2.99927530798058e-08</v>
@@ -7555,7 +7555,7 @@
         <v>2.992632528780846e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.995246224323182e-08</v>
+        <v>2.995246224323181e-08</v>
       </c>
       <c r="J2" t="n">
         <v>3.032571279759024e-08</v>
@@ -7564,13 +7564,13 @@
         <v>3.002439146811451e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.050756758343976e-08</v>
+        <v>3.050756758343975e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>3.01976610144075e-08</v>
+        <v>3.019766101440747e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.999180446622185e-08</v>
+        <v>2.999180446622184e-08</v>
       </c>
       <c r="O2" t="n">
         <v>2.991632238387045e-08</v>
@@ -7588,31 +7588,31 @@
         <v>3.00076938924092e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>2.992085236574771e-08</v>
+        <v>2.992085236574769e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>3.017730314038365e-08</v>
+        <v>3.017730314038362e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>2.308247072191956e-08</v>
+        <v>2.308247072191954e-08</v>
       </c>
       <c r="W2" t="n">
         <v>3.013886029396868e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>3.073792405574944e-08</v>
+        <v>3.073792405574943e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.14684379509681e-08</v>
+        <v>3.146843795096809e-08</v>
       </c>
       <c r="Z2" t="n">
         <v>2.997009603369342e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.003773525025151e-08</v>
+        <v>3.00377352502515e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.229495623115311e-08</v>
+        <v>3.22949562311531e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7622,85 +7622,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>2.143213204285954e-08</v>
+        <v>2.143213204285953e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>2.987059220594e-08</v>
+        <v>2.987059220593998e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>2.294449074304477e-08</v>
+        <v>2.294449074304478e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.99281776506918e-08</v>
+        <v>2.992817765069179e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.992817765085597e-08</v>
+        <v>2.992817765085596e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7710,22 +7710,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.248870553094851e-07</v>
+        <v>1.248870553094852e-07</v>
       </c>
       <c r="C4" t="n">
         <v>1.377972478162914e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>1.648119622783093e-07</v>
+        <v>1.648119622783094e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>6.274638153882806e-08</v>
+        <v>6.274638153882812e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>1.344010802160252e-07</v>
+        <v>1.344010802160251e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.06180883978761e-07</v>
+        <v>4.061808839787605e-07</v>
       </c>
       <c r="H4" t="n">
         <v>1.504288563713642e-07</v>
@@ -7734,52 +7734,52 @@
         <v>1.537297635093931e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>2.465167361920864e-07</v>
+        <v>2.465167361920865e-07</v>
       </c>
       <c r="K4" t="n">
         <v>1.773274634680581e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>2.78616304866312e-07</v>
+        <v>2.786163048663121e-07</v>
       </c>
       <c r="M4" t="n">
         <v>2.216275793862809e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.592644641595275e-07</v>
+        <v>1.592644641595278e-07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.39253999417012e-07</v>
+        <v>1.392539994170123e-07</v>
       </c>
       <c r="P4" t="n">
-        <v>2.136181990252108e-07</v>
+        <v>2.136181990252105e-07</v>
       </c>
       <c r="Q4" t="n">
         <v>1.498511248291968e-07</v>
       </c>
       <c r="R4" t="n">
-        <v>1.609417709122589e-07</v>
+        <v>1.609417709122591e-07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.593402356513577e-07</v>
+        <v>1.593402356513575e-07</v>
       </c>
       <c r="T4" t="n">
-        <v>1.454440835498678e-07</v>
+        <v>1.454440835498676e-07</v>
       </c>
       <c r="U4" t="n">
-        <v>2.02603166492175e-07</v>
+        <v>2.026031664921747e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51737243548281e-07</v>
+        <v>1.517372435482809e-07</v>
       </c>
       <c r="W4" t="n">
         <v>1.942232108665224e-07</v>
       </c>
       <c r="X4" t="n">
-        <v>3.494589355202796e-07</v>
+        <v>3.494589355202794e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.285699103077023e-07</v>
+        <v>5.285699103077013e-07</v>
       </c>
       <c r="Z4" t="n">
         <v>1.49466052943367e-07</v>
@@ -7788,7 +7788,7 @@
         <v>1.694573214445263e-07</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.924575062884165e-07</v>
+        <v>7.924575062884173e-07</v>
       </c>
     </row>
     <row r="5">
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.404725516723697e-07</v>
+        <v>1.404725516723698e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>2.258379165841918e-07</v>
+        <v>2.25837916584192e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>2.258379165841918e-07</v>
+        <v>2.25837916584192e-07</v>
       </c>
       <c r="E5" t="n">
         <v>1.803833778868357e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.537714778409252e-07</v>
+        <v>1.537714778409255e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>2.43538981103219e-07</v>
+        <v>2.435389811032191e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>2.258379165841918e-07</v>
+        <v>2.25837916584192e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>2.258379165841918e-07</v>
+        <v>2.25837916584192e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>2.257797303345391e-07</v>
+        <v>2.257797303345393e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>2.258379165841918e-07</v>
+        <v>2.25837916584192e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>2.258379165841918e-07</v>
+        <v>2.258379165841921e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.258379165841906e-07</v>
+        <v>2.258379165841909e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.592644641595275e-07</v>
+        <v>1.596654774662146e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>1.778502383080487e-07</v>
+        <v>1.778502383080491e-07</v>
       </c>
       <c r="P5" t="n">
-        <v>1.733927140195823e-07</v>
+        <v>1.733927140195827e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.236963090944352e-07</v>
+        <v>1.236963090944353e-07</v>
       </c>
       <c r="R5" t="n">
-        <v>2.258379165841918e-07</v>
+        <v>2.25837916584192e-07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.258379165841918e-07</v>
+        <v>2.25837916584192e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>2.258379165841918e-07</v>
+        <v>2.25837916584192e-07</v>
       </c>
       <c r="U5" t="n">
-        <v>1.841715714660317e-07</v>
+        <v>1.841715714660319e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>2.022060404698328e-07</v>
+        <v>2.022060404698331e-07</v>
       </c>
       <c r="W5" t="n">
-        <v>2.258546933367997e-07</v>
+        <v>2.258546933367999e-07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.31520214419809e-07</v>
+        <v>1.315202144198091e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.107136441382351e-07</v>
+        <v>3.107136441382353e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.388868461913527e-07</v>
+        <v>1.388868461913528e-07</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.258379165841918e-07</v>
+        <v>2.25837916584192e-07</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.150091783819918e-07</v>
+        <v>3.150091783819924e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7895,13 +7895,13 @@
         <v>1.306649963574168e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.244378072384205e-07</v>
+        <v>1.244378072384204e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>6.846549869500737e-08</v>
+        <v>6.846549869500743e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.306650059371373e-07</v>
+        <v>1.306650059371374e-07</v>
       </c>
       <c r="H6" t="n">
         <v>1.306649963574168e-07</v>
@@ -7910,7 +7910,7 @@
         <v>1.306649963574168e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.30606810107764e-07</v>
+        <v>1.306068101077641e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.306649963574168e-07</v>
@@ -7922,16 +7922,16 @@
         <v>1.306649963574168e-07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.592644641595275e-07</v>
+        <v>1.306649963574168e-07</v>
       </c>
       <c r="O6" t="n">
-        <v>1.396066089140401e-07</v>
+        <v>1.396066089140402e-07</v>
       </c>
       <c r="P6" t="n">
         <v>1.415512541494423e-07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.306650059371373e-07</v>
+        <v>1.306650059371374e-07</v>
       </c>
       <c r="R6" t="n">
         <v>1.306649963574168e-07</v>
@@ -7946,7 +7946,7 @@
         <v>1.306649963574168e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>1.615014237444635e-07</v>
+        <v>1.615014237444636e-07</v>
       </c>
       <c r="W6" t="n">
         <v>1.306649963574168e-07</v>
@@ -7974,61 +7974,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.895763779055941e-08</v>
+        <v>2.895763779055942e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.895828202795821e-08</v>
+        <v>2.895828202795819e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.827257077494586e-08</v>
+        <v>2.827257077494585e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.04525796870785e-08</v>
+        <v>2.045257968707848e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.901760576658681e-08</v>
+        <v>2.901760576658679e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.149273033729611e-08</v>
+        <v>2.149273033729609e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.86712372753037e-08</v>
+        <v>2.867123727530367e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.851150188151386e-08</v>
+        <v>2.851150188151383e-08</v>
       </c>
       <c r="J7" t="n">
         <v>2.587460689007393e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.808444368091916e-08</v>
+        <v>2.808444368091915e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.521238537197686e-08</v>
+        <v>2.521238537197684e-08</v>
       </c>
       <c r="M7" t="n">
         <v>2.708369802922065e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>2.827054584713728e-08</v>
+        <v>2.827054584713727e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>2.869761632995035e-08</v>
+        <v>2.869761632995036e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>2.666027341915595e-08</v>
+        <v>2.666027341915596e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.855143680361994e-08</v>
+        <v>2.855143680361997e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>2.838291711194229e-08</v>
+        <v>2.838291711194228e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.816145052410344e-08</v>
+        <v>2.816145052410343e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>2.869461061069018e-08</v>
+        <v>2.869461061069016e-08</v>
       </c>
       <c r="U7" t="n">
         <v>2.716195683111469e-08</v>
@@ -8037,16 +8037,16 @@
         <v>2.145842145257841e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>2.739658673151181e-08</v>
+        <v>2.739658673151177e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>2.390176211380456e-08</v>
+        <v>2.390176211380453e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.956644473184338e-08</v>
+        <v>1.956644473184337e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.838109303505361e-08</v>
+        <v>2.83810930350536e-08</v>
       </c>
       <c r="AA7" t="n">
         <v>2.799513533649531e-08</v>
@@ -8062,85 +8062,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.943126908355997e-08</v>
+        <v>2.943126908355995e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.94341645723022e-08</v>
+        <v>2.943416457230219e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.923944667516065e-08</v>
+        <v>2.923944667516064e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>2.10079700100801e-08</v>
+        <v>2.100797001008011e-08</v>
       </c>
       <c r="F8" t="n">
         <v>2.9452132926629e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.729029685055189e-08</v>
+        <v>2.72902968505519e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>2.935441341130091e-08</v>
+        <v>2.935441341130088e-08</v>
       </c>
       <c r="I8" t="n">
         <v>2.930787025350337e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>2.850752674442156e-08</v>
+        <v>2.850752674442155e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>2.918548663616174e-08</v>
+        <v>2.918548663616173e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>2.836186706821149e-08</v>
+        <v>2.836186706821147e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.890341372174473e-08</v>
+        <v>2.890341372174472e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.923757671297073e-08</v>
+        <v>2.923757671297072e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>2.935641306129213e-08</v>
+        <v>2.935641306129215e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>2.877099428624986e-08</v>
+        <v>2.877099428624985e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.931806029289302e-08</v>
+        <v>2.931806029289305e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>2.927195777935755e-08</v>
+        <v>2.927195777935753e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>2.920382741951154e-08</v>
+        <v>2.920382741951153e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>2.935957543132738e-08</v>
+        <v>2.935957543132734e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>2.891866385197864e-08</v>
+        <v>2.89186638519786e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>2.240630445893553e-08</v>
+        <v>2.240630445893551e-08</v>
       </c>
       <c r="W8" t="n">
         <v>2.898697835796552e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>2.799588578134425e-08</v>
+        <v>2.799588578134421e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.675381645200855e-08</v>
+        <v>2.675381645200849e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.926616760323723e-08</v>
+        <v>2.926616760323722e-08</v>
       </c>
       <c r="AA8" t="n">
         <v>2.915819483697708e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.540738317744271e-08</v>
+        <v>2.540738317744269e-08</v>
       </c>
     </row>
   </sheetData>
